--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -142,16 +142,22 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Tyler Phillips</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Tyler Phillips</t>
+    <t>&lt;6</t>
   </si>
   <si>
     <t>Jackson Jobe</t>
@@ -163,9 +169,6 @@
     <t>Ian Seymour</t>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Andrew Alvarez</t>
   </si>
   <si>
@@ -274,16 +277,16 @@
     <t>Michael King</t>
   </si>
   <si>
+    <t>Adrian Houser</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
+  </si>
+  <si>
     <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Adrian Houser</t>
   </si>
 </sst>
 </file>
@@ -800,10 +803,10 @@
         <v>6.5</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>-145</v>
+        <v>-135</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -848,10 +851,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2107</v>
+        <v>0.2391</v>
       </c>
       <c r="U2">
-        <v>0.1988</v>
+        <v>0.2122</v>
       </c>
       <c r="V2">
         <v>9</v>
@@ -860,10 +863,10 @@
         <v>0.2307</v>
       </c>
       <c r="X2">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y2">
-        <v>0.936</v>
+        <v>0.8824</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -872,7 +875,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.1</v>
+        <v>6.51</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -881,13 +884,13 @@
         <v>0.2958</v>
       </c>
       <c r="AG2">
-        <v>0.9575</v>
+        <v>1.0836</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.1</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -901,28 +904,70 @@
         <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-105</v>
+        <v>-120</v>
       </c>
       <c r="E3">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>823826</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>0.182</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>4.31</v>
+      </c>
+      <c r="Q3">
+        <v>0.2</v>
+      </c>
+      <c r="R3">
+        <v>0.333</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="T3">
+        <v>0.1877</v>
+      </c>
+      <c r="U3">
+        <v>0.1904</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2139</v>
+      </c>
+      <c r="X3">
+        <v>0.2207</v>
+      </c>
+      <c r="Y3">
+        <v>0.9634</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -930,8 +975,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>3.04</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AF3">
+        <v>0.188</v>
+      </c>
+      <c r="AG3">
+        <v>0.8503</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>3.04</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -939,19 +999,19 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E4">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -983,19 +1043,19 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
+        <v>-123</v>
+      </c>
+      <c r="E5">
         <v>-104</v>
       </c>
-      <c r="E5">
-        <v>-107</v>
-      </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>824233</v>
@@ -1013,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0.2922</v>
@@ -1034,7 +1094,7 @@
         <v>0.357</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T5">
         <v>0.1922</v>
@@ -1049,7 +1109,7 @@
         <v>0.2277</v>
       </c>
       <c r="X5">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y5">
         <v>0.9864</v>
@@ -1061,22 +1121,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="AE5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>0.3069</v>
       </c>
       <c r="AG5">
-        <v>0.8737</v>
+        <v>0.871</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1084,7 +1144,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1093,10 +1153,10 @@
         <v>-130</v>
       </c>
       <c r="E6">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>822693</v>
@@ -1135,7 +1195,7 @@
         <v>0.351</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T6">
         <v>0.2285</v>
@@ -1150,7 +1210,7 @@
         <v>0.2478</v>
       </c>
       <c r="X6">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y6">
         <v>1.0329</v>
@@ -1162,22 +1222,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="AE6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6">
         <v>0.2002</v>
       </c>
       <c r="AG6">
-        <v>1.0387</v>
+        <v>1.0355</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1185,7 +1245,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1197,7 +1257,7 @@
         <v>-143</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
         <v>44</v>
@@ -1229,19 +1289,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-143</v>
+        <v>-135</v>
       </c>
       <c r="E8">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>823505</v>
@@ -1280,7 +1340,7 @@
         <v>0.338</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T8">
         <v>0.2188</v>
@@ -1295,7 +1355,7 @@
         <v>0.2189</v>
       </c>
       <c r="X8">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y8">
         <v>0.996</v>
@@ -1307,22 +1367,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="AE8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF8">
         <v>0.2338</v>
       </c>
       <c r="AG8">
-        <v>0.9945</v>
+        <v>0.9915</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1330,19 +1390,19 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>3.5</v>
       </c>
       <c r="D9">
-        <v>-120</v>
+        <v>-116</v>
       </c>
       <c r="E9">
         <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>822773</v>
@@ -1381,7 +1441,7 @@
         <v>0.375</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T9">
         <v>0.1966</v>
@@ -1396,7 +1456,7 @@
         <v>0.189</v>
       </c>
       <c r="X9">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y9">
         <v>0.9839</v>
@@ -1408,22 +1468,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AE9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF9">
         <v>0.1652</v>
       </c>
       <c r="AG9">
-        <v>0.8936</v>
+        <v>0.8909</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1431,25 +1491,25 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>3.5</v>
       </c>
       <c r="D10">
-        <v>-146</v>
+        <v>-148</v>
       </c>
       <c r="E10">
         <v>126</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>822773</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I10">
         <v>4.1</v>
@@ -1482,7 +1542,7 @@
         <v>0.333</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T10">
         <v>0.1657</v>
@@ -1497,7 +1557,7 @@
         <v>0.208</v>
       </c>
       <c r="X10">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y10">
         <v>0.9543</v>
@@ -1509,22 +1569,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AE10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF10">
         <v>0.1656</v>
       </c>
       <c r="AG10">
-        <v>0.753</v>
+        <v>0.7507</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1532,19 +1592,19 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-160</v>
+        <v>-155</v>
       </c>
       <c r="E11">
         <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
         <v>44</v>
@@ -1576,19 +1636,19 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-118</v>
+        <v>-125</v>
       </c>
       <c r="E12">
         <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>823585</v>
@@ -1627,7 +1687,7 @@
         <v>0.317</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T12">
         <v>0.2358</v>
@@ -1642,7 +1702,7 @@
         <v>0.2322</v>
       </c>
       <c r="X12">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y12">
         <v>0.985</v>
@@ -1654,7 +1714,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1663,13 +1723,13 @@
         <v>0.2959</v>
       </c>
       <c r="AG12">
-        <v>1.0715</v>
+        <v>1.0683</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1677,19 +1737,19 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>5.5</v>
       </c>
       <c r="D13">
-        <v>-148</v>
+        <v>-160</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>824881</v>
@@ -1728,7 +1788,7 @@
         <v>0.336</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T13">
         <v>0.2326</v>
@@ -1743,7 +1803,7 @@
         <v>0.2195</v>
       </c>
       <c r="X13">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y13">
         <v>0.9815</v>
@@ -1755,22 +1815,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="AE13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF13">
         <v>0.3329</v>
       </c>
       <c r="AG13">
-        <v>1.0572</v>
+        <v>1.054</v>
       </c>
       <c r="AH13">
         <v>-0.6</v>
       </c>
       <c r="AM13">
-        <v>6.7</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1778,19 +1838,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>4.5</v>
       </c>
       <c r="D14">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>-152</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>824881</v>
@@ -1829,7 +1889,7 @@
         <v>0.379</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T14">
         <v>0.311</v>
@@ -1844,7 +1904,7 @@
         <v>0.2072</v>
       </c>
       <c r="X14">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y14">
         <v>0.9984</v>
@@ -1856,7 +1916,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -1865,13 +1925,13 @@
         <v>0.1926</v>
       </c>
       <c r="AG14">
-        <v>1.4136</v>
+        <v>1.4093</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1879,19 +1939,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="E15">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>824556</v>
@@ -1930,7 +1990,7 @@
         <v>0.377</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T15">
         <v>0.2379</v>
@@ -1945,7 +2005,7 @@
         <v>0.2428</v>
       </c>
       <c r="X15">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y15">
         <v>1.0234</v>
@@ -1957,22 +2017,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="AE15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF15">
         <v>0.1895</v>
       </c>
       <c r="AG15">
-        <v>1.0815</v>
+        <v>1.0782</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -1980,19 +2040,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16">
         <v>6.5</v>
       </c>
       <c r="D16">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="E16">
-        <v>-109</v>
+        <v>-105</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>824556</v>
@@ -2031,7 +2091,7 @@
         <v>0.32</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T16">
         <v>0.2313</v>
@@ -2046,7 +2106,7 @@
         <v>0.2377</v>
       </c>
       <c r="X16">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y16">
         <v>1.0329</v>
@@ -2058,22 +2118,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="AE16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF16">
         <v>0.3048</v>
       </c>
       <c r="AG16">
-        <v>1.0513</v>
+        <v>1.0481</v>
       </c>
       <c r="AH16">
         <v>-0.6</v>
       </c>
       <c r="AM16">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2081,7 +2141,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2090,10 +2150,10 @@
         <v>-120</v>
       </c>
       <c r="E17">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>823016</v>
@@ -2132,7 +2192,7 @@
         <v>0.355</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T17">
         <v>0.201</v>
@@ -2147,7 +2207,7 @@
         <v>0.2142</v>
       </c>
       <c r="X17">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y17">
         <v>0.9847</v>
@@ -2159,22 +2219,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AE17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF17">
         <v>0.1477</v>
       </c>
       <c r="AG17">
-        <v>0.9137</v>
+        <v>0.9109</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2182,19 +2242,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D18">
-        <v>-146</v>
+        <v>116</v>
       </c>
       <c r="E18">
-        <v>121</v>
+        <v>-138</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>823989</v>
@@ -2233,7 +2293,7 @@
         <v>0.361</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T18">
         <v>0.2472</v>
@@ -2248,7 +2308,7 @@
         <v>0.2511</v>
       </c>
       <c r="X18">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y18">
         <v>1.0421</v>
@@ -2260,22 +2320,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>9.8</v>
+        <v>9.77</v>
       </c>
       <c r="AE18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF18">
         <v>0.3506</v>
       </c>
       <c r="AG18">
-        <v>1.1233</v>
+        <v>1.1199</v>
       </c>
       <c r="AH18">
         <v>-0.6</v>
       </c>
       <c r="AM18">
-        <v>9.2</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2283,7 +2343,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2292,10 +2352,10 @@
         <v>130</v>
       </c>
       <c r="E19">
-        <v>-164</v>
+        <v>-155</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>823989</v>
@@ -2334,7 +2394,7 @@
         <v>0.336</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T19">
         <v>0.2037</v>
@@ -2349,7 +2409,7 @@
         <v>0.2107</v>
       </c>
       <c r="X19">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y19">
         <v>0.9595</v>
@@ -2361,22 +2421,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="AE19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF19">
         <v>0.2376</v>
       </c>
       <c r="AG19">
-        <v>0.9258</v>
+        <v>0.9229</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2384,19 +2444,19 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E20">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>825042</v>
@@ -2435,7 +2495,7 @@
         <v>0.381</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T20">
         <v>0.2167</v>
@@ -2450,7 +2510,7 @@
         <v>0.2173</v>
       </c>
       <c r="X20">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y20">
         <v>0.9878</v>
@@ -2462,22 +2522,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="AE20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF20">
         <v>0.1803</v>
       </c>
       <c r="AG20">
-        <v>0.9848</v>
+        <v>0.9818</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2485,19 +2545,19 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>3.5</v>
       </c>
       <c r="D21">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E21">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21">
         <v>825042</v>
@@ -2536,7 +2596,7 @@
         <v>0.355</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T21">
         <v>0.1678</v>
@@ -2551,7 +2611,7 @@
         <v>0.1976</v>
       </c>
       <c r="X21">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y21">
         <v>0.9284</v>
@@ -2563,22 +2623,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AE21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF21">
         <v>0.1773</v>
       </c>
       <c r="AG21">
-        <v>0.7628</v>
+        <v>0.7605</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2586,7 +2646,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2598,7 +2658,7 @@
         <v>-104</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>824962</v>
@@ -2637,7 +2697,7 @@
         <v>0.371</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T22">
         <v>0.2579</v>
@@ -2652,7 +2712,7 @@
         <v>0.2132</v>
       </c>
       <c r="X22">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y22">
         <v>1.0394</v>
@@ -2664,22 +2724,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>7.5</v>
+        <v>7.48</v>
       </c>
       <c r="AE22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF22">
         <v>0.2571</v>
       </c>
       <c r="AG22">
-        <v>1.172</v>
+        <v>1.1685</v>
       </c>
       <c r="AH22">
         <v>-0.6</v>
       </c>
       <c r="AM22">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2687,19 +2747,19 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>-155</v>
+        <v>-140</v>
       </c>
       <c r="E23">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>824962</v>
@@ -2738,7 +2798,7 @@
         <v>0.367</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T23">
         <v>0.182</v>
@@ -2753,7 +2813,7 @@
         <v>0.2191</v>
       </c>
       <c r="X23">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y23">
         <v>0.9797</v>
@@ -2765,22 +2825,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="AE23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF23">
         <v>0.2397</v>
       </c>
       <c r="AG23">
-        <v>0.8271</v>
+        <v>0.8245</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2788,19 +2848,19 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>5.5</v>
       </c>
       <c r="D24">
-        <v>-127</v>
+        <v>-120</v>
       </c>
       <c r="E24">
-        <v>106</v>
+        <v>-104</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24">
         <v>823098</v>
@@ -2839,7 +2899,7 @@
         <v>0.371</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T24">
         <v>0.2402</v>
@@ -2854,7 +2914,7 @@
         <v>0.2254</v>
       </c>
       <c r="X24">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y24">
         <v>1.0109</v>
@@ -2866,7 +2926,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -2875,13 +2935,13 @@
         <v>0.2618</v>
       </c>
       <c r="AG24">
-        <v>1.0915</v>
+        <v>1.0882</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2889,19 +2949,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="E25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>823098</v>
@@ -2940,7 +3000,7 @@
         <v>0.355</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T25">
         <v>0.1484</v>
@@ -2955,7 +3015,7 @@
         <v>0.2203</v>
       </c>
       <c r="X25">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y25">
         <v>0.9783</v>
@@ -2967,22 +3027,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AE25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF25">
         <v>0.1705</v>
       </c>
       <c r="AG25">
-        <v>0.6745</v>
+        <v>0.6724</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2990,19 +3050,19 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>124</v>
+        <v>-154</v>
       </c>
       <c r="E26">
-        <v>-144</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>823259</v>
@@ -3041,7 +3101,7 @@
         <v>0.351</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T26">
         <v>0.1828</v>
@@ -3056,7 +3116,7 @@
         <v>0.2161</v>
       </c>
       <c r="X26">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y26">
         <v>0.9905</v>
@@ -3068,22 +3128,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.46</v>
+        <v>5.44</v>
       </c>
       <c r="AE26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF26">
         <v>0.3009</v>
       </c>
       <c r="AG26">
-        <v>0.8309</v>
+        <v>0.8283</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>5.46</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3091,19 +3151,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>5.5</v>
       </c>
       <c r="D27">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="E27">
-        <v>-114</v>
+        <v>-111</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>823259</v>
@@ -3142,7 +3202,7 @@
         <v>0.373</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T27">
         <v>0.1979</v>
@@ -3157,7 +3217,7 @@
         <v>0.2371</v>
       </c>
       <c r="X27">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y27">
         <v>1.0167</v>
@@ -3169,22 +3229,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="AE27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF27">
         <v>0.2099</v>
       </c>
       <c r="AG27">
-        <v>0.8995</v>
+        <v>0.8968</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3192,19 +3252,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="C28">
+        <v>3.5</v>
+      </c>
+      <c r="D28">
+        <v>-140</v>
+      </c>
+      <c r="E28">
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G28">
-        <v>823585</v>
+        <v>823181</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3213,46 +3282,46 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>0.18</v>
+        <v>0.1573</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="P28">
-        <v>3.97</v>
+        <v>4.3</v>
       </c>
       <c r="Q28">
-        <v>0.1681</v>
+        <v>0.2529</v>
       </c>
       <c r="R28">
-        <v>0.361</v>
+        <v>0.303</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T28">
-        <v>0.2286</v>
+        <v>0.3635</v>
       </c>
       <c r="U28">
-        <v>0.2264</v>
+        <v>0.2882</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2197</v>
+        <v>0.2558</v>
       </c>
       <c r="X28">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y28">
-        <v>1.0023</v>
+        <v>1.046</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3261,22 +3330,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.07</v>
+        <v>6.43</v>
       </c>
       <c r="AE28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.1757</v>
+        <v>0.1809</v>
       </c>
       <c r="AG28">
-        <v>1.0391</v>
+        <v>1.647</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.07</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3284,7 +3353,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>116</v>
+      </c>
+      <c r="E29">
+        <v>-133</v>
       </c>
       <c r="F29" t="s">
         <v>89</v>
@@ -3305,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>0.1835</v>
@@ -3326,7 +3404,7 @@
         <v>0.392</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T29">
         <v>0.2064</v>
@@ -3341,7 +3419,7 @@
         <v>0.2044</v>
       </c>
       <c r="X29">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y29">
         <v>0.9925</v>
@@ -3353,22 +3431,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="AE29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF29">
         <v>0.1693</v>
       </c>
       <c r="AG29">
-        <v>0.9381</v>
+        <v>0.9353</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3376,19 +3454,19 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="G30">
-        <v>823181</v>
+        <v>823585</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3400,43 +3478,43 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.1573</v>
+        <v>0.18</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="P30">
-        <v>4.3</v>
+        <v>3.97</v>
       </c>
       <c r="Q30">
-        <v>0.2529</v>
+        <v>0.1681</v>
       </c>
       <c r="R30">
-        <v>0.303</v>
+        <v>0.361</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T30">
-        <v>0.3635</v>
+        <v>0.2286</v>
       </c>
       <c r="U30">
-        <v>0.2882</v>
+        <v>0.2264</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>0.2558</v>
+        <v>0.2197</v>
       </c>
       <c r="X30">
-        <v>0.22</v>
+        <v>0.2207</v>
       </c>
       <c r="Y30">
-        <v>1.046</v>
+        <v>1.0023</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3445,22 +3523,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>6.45</v>
+        <v>4.05</v>
       </c>
       <c r="AE30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF30">
-        <v>0.1809</v>
+        <v>0.1757</v>
       </c>
       <c r="AG30">
-        <v>1.652</v>
+        <v>1.036</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>6.45</v>
+        <v>4.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -154,27 +154,27 @@
     <t>Tyler Phillips</t>
   </si>
   <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Jackson Jobe</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Ian Seymour</t>
+  </si>
+  <si>
+    <t>Andrew Alvarez</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Jackson Jobe</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Ian Seymour</t>
-  </si>
-  <si>
-    <t>Andrew Alvarez</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
     <t>Ethan Pecko</t>
   </si>
   <si>
@@ -205,6 +205,9 @@
     <t>Kyle Harrison</t>
   </si>
   <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
     <t>Tyler Glasnow</t>
   </si>
   <si>
@@ -217,37 +220,49 @@
     <t>Bryce Elder</t>
   </si>
   <si>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
     <t>Anthony Kay</t>
   </si>
   <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
     <t>Chris Bassitt</t>
   </si>
   <si>
     <t>Baltimore Orioles @ St. Louis Cardinals</t>
   </si>
   <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
     <t>Gavin Williams</t>
   </si>
   <si>
     <t>Cleveland Guardians @ Los Angeles Angels</t>
   </si>
   <si>
-    <t>Walbert Urena</t>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
   </si>
   <si>
     <t>Brandon Pfaadt</t>
   </si>
   <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Michael King</t>
   </si>
   <si>
     <t>Taj Bradley</t>
@@ -268,25 +283,13 @@
     <t>George Kirby</t>
   </si>
   <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Michael King</t>
+    <t>Brady Singer</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
   </si>
   <si>
     <t>Adrian Houser</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
   </si>
 </sst>
 </file>
@@ -667,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM30"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -803,10 +806,10 @@
         <v>6.5</v>
       </c>
       <c r="D2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>-135</v>
+        <v>-137</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -863,7 +866,7 @@
         <v>0.2307</v>
       </c>
       <c r="X2">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y2">
         <v>0.8824</v>
@@ -875,7 +878,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.51</v>
+        <v>6.65</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -884,13 +887,13 @@
         <v>0.2958</v>
       </c>
       <c r="AG2">
-        <v>1.0836</v>
+        <v>1.1069</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.51</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,7 +910,7 @@
         <v>-120</v>
       </c>
       <c r="E3">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -949,13 +952,13 @@
         <v>0.333</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1877</v>
+        <v>0.1854</v>
       </c>
       <c r="U3">
-        <v>0.1904</v>
+        <v>0.199</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -964,10 +967,10 @@
         <v>0.2139</v>
       </c>
       <c r="X3">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y3">
-        <v>0.9634</v>
+        <v>0.9777</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -976,22 +979,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AE3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF3">
         <v>0.188</v>
       </c>
       <c r="AG3">
-        <v>0.8503</v>
+        <v>0.8582</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -999,19 +1002,19 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4">
         <v>-132</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -1043,19 +1046,19 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="E5">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>824233</v>
@@ -1094,13 +1097,13 @@
         <v>0.357</v>
       </c>
       <c r="S5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1922</v>
+        <v>0.1947</v>
       </c>
       <c r="U5">
-        <v>0.1872</v>
+        <v>0.1919</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1109,10 +1112,10 @@
         <v>0.2277</v>
       </c>
       <c r="X5">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y5">
-        <v>0.9864</v>
+        <v>0.9633</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1121,22 +1124,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="AE5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF5">
         <v>0.3069</v>
       </c>
       <c r="AG5">
-        <v>0.871</v>
+        <v>0.9011</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1144,7 +1147,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1156,7 +1159,7 @@
         <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>822693</v>
@@ -1195,7 +1198,7 @@
         <v>0.351</v>
       </c>
       <c r="S6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T6">
         <v>0.2285</v>
@@ -1210,7 +1213,7 @@
         <v>0.2478</v>
       </c>
       <c r="X6">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y6">
         <v>1.0329</v>
@@ -1222,22 +1225,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="AE6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF6">
         <v>0.2002</v>
       </c>
       <c r="AG6">
-        <v>1.0355</v>
+        <v>1.0579</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1340,7 +1343,7 @@
         <v>0.338</v>
       </c>
       <c r="S8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T8">
         <v>0.2188</v>
@@ -1355,7 +1358,7 @@
         <v>0.2189</v>
       </c>
       <c r="X8">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y8">
         <v>0.996</v>
@@ -1367,22 +1370,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
       <c r="AE8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF8">
         <v>0.2338</v>
       </c>
       <c r="AG8">
-        <v>0.9915</v>
+        <v>1.0128</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1396,10 +1399,10 @@
         <v>3.5</v>
       </c>
       <c r="D9">
-        <v>-116</v>
+        <v>-130</v>
       </c>
       <c r="E9">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -1441,13 +1444,13 @@
         <v>0.375</v>
       </c>
       <c r="S9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.1966</v>
+        <v>0.2005</v>
       </c>
       <c r="U9">
-        <v>0.1835</v>
+        <v>0.1876</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1456,10 +1459,10 @@
         <v>0.189</v>
       </c>
       <c r="X9">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y9">
-        <v>0.9839</v>
+        <v>0.9732</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1468,22 +1471,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AE9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF9">
         <v>0.1652</v>
       </c>
       <c r="AG9">
-        <v>0.8909</v>
+        <v>0.9281</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1497,10 +1500,10 @@
         <v>3.5</v>
       </c>
       <c r="D10">
-        <v>-148</v>
+        <v>-140</v>
       </c>
       <c r="E10">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -1542,13 +1545,13 @@
         <v>0.333</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1657</v>
+        <v>0.1732</v>
       </c>
       <c r="U10">
-        <v>0.1814</v>
+        <v>0.1849</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1557,10 +1560,10 @@
         <v>0.208</v>
       </c>
       <c r="X10">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y10">
-        <v>0.9543</v>
+        <v>0.8979</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1569,22 +1572,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AE10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF10">
         <v>0.1656</v>
       </c>
       <c r="AG10">
-        <v>0.7507</v>
+        <v>0.8017</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1598,10 +1601,10 @@
         <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-155</v>
+        <v>-140</v>
       </c>
       <c r="E11">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
@@ -1642,7 +1645,7 @@
         <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -1687,25 +1690,25 @@
         <v>0.317</v>
       </c>
       <c r="S12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2358</v>
+        <v>0.1933</v>
       </c>
       <c r="U12">
-        <v>0.2277</v>
+        <v>0.2049</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>0.2322</v>
       </c>
       <c r="X12">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y12">
-        <v>0.985</v>
+        <v>0.9313</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1714,22 +1717,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.26</v>
+        <v>4.96</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF12">
         <v>0.2959</v>
       </c>
       <c r="AG12">
-        <v>1.0683</v>
+        <v>0.8947</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>6.26</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1739,26 +1742,17 @@
       <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-      <c r="D13">
-        <v>-160</v>
-      </c>
-      <c r="E13">
-        <v>130</v>
-      </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>824881</v>
+        <v>823585</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1767,46 +1761,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>0.3311</v>
+        <v>0.18</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P13">
-        <v>3.73</v>
+        <v>3.97</v>
       </c>
       <c r="Q13">
-        <v>0.3366</v>
+        <v>0.1681</v>
       </c>
       <c r="R13">
-        <v>0.336</v>
+        <v>0.361</v>
       </c>
       <c r="S13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2326</v>
+        <v>0.2334</v>
       </c>
       <c r="U13">
-        <v>0.2283</v>
+        <v>0.2268</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2195</v>
+        <v>0.2197</v>
       </c>
       <c r="X13">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y13">
-        <v>0.9815</v>
+        <v>0.9845</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1815,22 +1809,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.28</v>
+        <v>4.15</v>
       </c>
       <c r="AE13" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="AF13">
-        <v>0.3329</v>
+        <v>0.1757</v>
       </c>
       <c r="AG13">
-        <v>1.054</v>
+        <v>1.0803</v>
       </c>
       <c r="AH13">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.68</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1838,19 +1832,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>128</v>
+        <v>-160</v>
       </c>
       <c r="E14">
-        <v>-152</v>
+        <v>130</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>824881</v>
@@ -1871,43 +1865,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1952</v>
+        <v>0.3311</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="P14">
-        <v>4.21</v>
+        <v>3.73</v>
       </c>
       <c r="Q14">
-        <v>0.1885</v>
+        <v>0.3366</v>
       </c>
       <c r="R14">
-        <v>0.379</v>
+        <v>0.336</v>
       </c>
       <c r="S14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.311</v>
+        <v>0.2367</v>
       </c>
       <c r="U14">
-        <v>0.2072</v>
+        <v>0.2268</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2072</v>
+        <v>0.2195</v>
       </c>
       <c r="X14">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y14">
-        <v>0.9984</v>
+        <v>0.9769</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1916,22 +1910,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.54</v>
+        <v>7.53</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="AF14">
-        <v>0.1926</v>
+        <v>0.3329</v>
       </c>
       <c r="AG14">
-        <v>1.4093</v>
+        <v>1.0954</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM14">
-        <v>6.54</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1945,22 +1939,22 @@
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-120</v>
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>105</v>
+        <v>-152</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G15">
-        <v>824556</v>
+        <v>824881</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1972,67 +1966,67 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1841</v>
+        <v>0.1952</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P15">
-        <v>4.44</v>
+        <v>4.21</v>
       </c>
       <c r="Q15">
-        <v>0.1983</v>
+        <v>0.1885</v>
       </c>
       <c r="R15">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="S15" t="s">
+        <v>43</v>
+      </c>
+      <c r="T15">
+        <v>0.2135</v>
+      </c>
+      <c r="U15">
+        <v>0.1988</v>
+      </c>
+      <c r="V15">
+        <v>9</v>
+      </c>
+      <c r="W15">
+        <v>0.2072</v>
+      </c>
+      <c r="X15">
+        <v>0.216</v>
+      </c>
+      <c r="Y15">
+        <v>0.9474</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD15">
+        <v>4.35</v>
+      </c>
+      <c r="AE15" t="s">
         <v>47</v>
       </c>
-      <c r="T15">
-        <v>0.2379</v>
-      </c>
-      <c r="U15">
-        <v>0.238</v>
-      </c>
-      <c r="V15">
-        <v>8</v>
-      </c>
-      <c r="W15">
-        <v>0.2428</v>
-      </c>
-      <c r="X15">
-        <v>0.2207</v>
-      </c>
-      <c r="Y15">
-        <v>1.0234</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD15">
-        <v>4.65</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>48</v>
-      </c>
       <c r="AF15">
-        <v>0.1895</v>
+        <v>0.1926</v>
       </c>
       <c r="AG15">
-        <v>1.0782</v>
+        <v>0.9882</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.65</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2040,7 +2034,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>6.5</v>
@@ -2052,7 +2046,7 @@
         <v>-105</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>824556</v>
@@ -2091,7 +2085,7 @@
         <v>0.32</v>
       </c>
       <c r="S16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T16">
         <v>0.2313</v>
@@ -2106,7 +2100,7 @@
         <v>0.2377</v>
       </c>
       <c r="X16">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y16">
         <v>1.0329</v>
@@ -2118,22 +2112,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>7.12</v>
+        <v>7.28</v>
       </c>
       <c r="AE16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF16">
         <v>0.3048</v>
       </c>
       <c r="AG16">
-        <v>1.0481</v>
+        <v>1.0707</v>
       </c>
       <c r="AH16">
         <v>-0.6</v>
       </c>
       <c r="AM16">
-        <v>6.52</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2144,25 +2138,25 @@
         <v>71</v>
       </c>
       <c r="C17">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D17">
         <v>-120</v>
       </c>
       <c r="E17">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>823016</v>
+        <v>824556</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2174,43 +2168,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1489</v>
+        <v>0.1841</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="P17">
-        <v>4.59</v>
+        <v>4.44</v>
       </c>
       <c r="Q17">
-        <v>0.1455</v>
+        <v>0.1983</v>
       </c>
       <c r="R17">
-        <v>0.355</v>
+        <v>0.377</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T17">
-        <v>0.201</v>
+        <v>0.2379</v>
       </c>
       <c r="U17">
-        <v>0.2008</v>
+        <v>0.238</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>0.2142</v>
+        <v>0.2428</v>
       </c>
       <c r="X17">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y17">
-        <v>0.9847</v>
+        <v>1.0234</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2219,22 +2213,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
       <c r="AE17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF17">
-        <v>0.1477</v>
+        <v>0.1895</v>
       </c>
       <c r="AG17">
-        <v>0.9109</v>
+        <v>1.1014</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2242,28 +2236,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>3.5</v>
+      </c>
+      <c r="D18">
+        <v>-120</v>
+      </c>
+      <c r="E18">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
         <v>73</v>
       </c>
-      <c r="C18">
-        <v>8.5</v>
-      </c>
-      <c r="D18">
-        <v>116</v>
-      </c>
-      <c r="E18">
-        <v>-138</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
-      </c>
       <c r="G18">
-        <v>823989</v>
+        <v>823016</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2272,70 +2266,70 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>0.3237</v>
+        <v>0.1489</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P18">
-        <v>4.02</v>
+        <v>4.59</v>
       </c>
       <c r="Q18">
-        <v>0.3982</v>
+        <v>0.1455</v>
       </c>
       <c r="R18">
-        <v>0.361</v>
+        <v>0.355</v>
       </c>
       <c r="S18" t="s">
+        <v>43</v>
+      </c>
+      <c r="T18">
+        <v>0.1757</v>
+      </c>
+      <c r="U18">
+        <v>0.1924</v>
+      </c>
+      <c r="V18">
+        <v>8</v>
+      </c>
+      <c r="W18">
+        <v>0.2142</v>
+      </c>
+      <c r="X18">
+        <v>0.216</v>
+      </c>
+      <c r="Y18">
+        <v>0.9745</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD18">
+        <v>2.55</v>
+      </c>
+      <c r="AE18" t="s">
         <v>47</v>
       </c>
-      <c r="T18">
-        <v>0.2472</v>
-      </c>
-      <c r="U18">
-        <v>0.2397</v>
-      </c>
-      <c r="V18">
-        <v>9</v>
-      </c>
-      <c r="W18">
-        <v>0.2511</v>
-      </c>
-      <c r="X18">
-        <v>0.2207</v>
-      </c>
-      <c r="Y18">
-        <v>1.0421</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD18">
-        <v>9.77</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>66</v>
-      </c>
       <c r="AF18">
-        <v>0.3506</v>
+        <v>0.1477</v>
       </c>
       <c r="AG18">
-        <v>1.1199</v>
+        <v>0.8133</v>
       </c>
       <c r="AH18">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>9.17</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2343,28 +2337,19 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19">
-        <v>4.5</v>
-      </c>
-      <c r="D19">
-        <v>130</v>
-      </c>
-      <c r="E19">
-        <v>-155</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19">
-        <v>823989</v>
+        <v>823016</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2373,46 +2358,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>0.2276</v>
+        <v>0.2311</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P19">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
-        <v>0.2574</v>
+        <v>0.2885</v>
       </c>
       <c r="R19">
-        <v>0.336</v>
+        <v>0.342</v>
       </c>
       <c r="S19" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T19">
-        <v>0.2037</v>
+        <v>0.2528</v>
       </c>
       <c r="U19">
-        <v>0.1828</v>
+        <v>0.2394</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2107</v>
+        <v>0.2573</v>
       </c>
       <c r="X19">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y19">
-        <v>0.9595</v>
+        <v>1.0429</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2421,22 +2406,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.73</v>
+        <v>6.62</v>
       </c>
       <c r="AE19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2376</v>
+        <v>0.2507</v>
       </c>
       <c r="AG19">
-        <v>0.9229</v>
+        <v>1.1701</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.73</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2444,22 +2429,22 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D20">
         <v>116</v>
       </c>
       <c r="E20">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20">
-        <v>825042</v>
+        <v>823989</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
@@ -2474,46 +2459,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>0.1712</v>
+        <v>0.3237</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P20">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="Q20">
-        <v>0.1951</v>
+        <v>0.3982</v>
       </c>
       <c r="R20">
-        <v>0.381</v>
+        <v>0.361</v>
       </c>
       <c r="S20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T20">
-        <v>0.2167</v>
+        <v>0.2472</v>
       </c>
       <c r="U20">
-        <v>0.2155</v>
+        <v>0.2397</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2173</v>
+        <v>0.2511</v>
       </c>
       <c r="X20">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y20">
-        <v>0.9878</v>
+        <v>1.0421</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2522,22 +2507,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.24</v>
+        <v>9.98</v>
       </c>
       <c r="AE20" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="AF20">
-        <v>0.1803</v>
+        <v>0.3506</v>
       </c>
       <c r="AG20">
-        <v>0.9818</v>
+        <v>1.144</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM20">
-        <v>4.24</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2545,28 +2530,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>-132</v>
+        <v>-155</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21">
-        <v>825042</v>
+        <v>823989</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2575,46 +2560,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>0.1799</v>
+        <v>0.2276</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="P21">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="Q21">
-        <v>0.1727</v>
+        <v>0.2574</v>
       </c>
       <c r="R21">
-        <v>0.355</v>
+        <v>0.336</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T21">
-        <v>0.1678</v>
+        <v>0.2037</v>
       </c>
       <c r="U21">
-        <v>0.1685</v>
+        <v>0.1828</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.1976</v>
+        <v>0.2107</v>
       </c>
       <c r="X21">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y21">
-        <v>0.9284</v>
+        <v>0.9595</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2623,22 +2608,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>2.9</v>
+        <v>4.83</v>
       </c>
       <c r="AE21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF21">
-        <v>0.1773</v>
+        <v>0.2376</v>
       </c>
       <c r="AG21">
-        <v>0.7605</v>
+        <v>0.9428</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>2.9</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2646,28 +2631,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>3.5</v>
+      </c>
+      <c r="D22">
+        <v>107</v>
+      </c>
+      <c r="E22">
+        <v>-132</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="C22">
-        <v>5.5</v>
-      </c>
-      <c r="D22">
-        <v>-105</v>
-      </c>
-      <c r="E22">
-        <v>-104</v>
-      </c>
-      <c r="F22" t="s">
-        <v>80</v>
-      </c>
       <c r="G22">
-        <v>824962</v>
+        <v>825042</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2679,67 +2664,67 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2638</v>
+        <v>0.1799</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P22">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="Q22">
-        <v>0.2458</v>
+        <v>0.1727</v>
       </c>
       <c r="R22">
-        <v>0.371</v>
+        <v>0.355</v>
       </c>
       <c r="S22" t="s">
+        <v>53</v>
+      </c>
+      <c r="T22">
+        <v>0.1678</v>
+      </c>
+      <c r="U22">
+        <v>0.1685</v>
+      </c>
+      <c r="V22">
+        <v>9</v>
+      </c>
+      <c r="W22">
+        <v>0.1976</v>
+      </c>
+      <c r="X22">
+        <v>0.216</v>
+      </c>
+      <c r="Y22">
+        <v>0.9284</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD22">
+        <v>2.96</v>
+      </c>
+      <c r="AE22" t="s">
         <v>47</v>
       </c>
-      <c r="T22">
-        <v>0.2579</v>
-      </c>
-      <c r="U22">
-        <v>0.2281</v>
-      </c>
-      <c r="V22">
-        <v>8</v>
-      </c>
-      <c r="W22">
-        <v>0.2132</v>
-      </c>
-      <c r="X22">
-        <v>0.2207</v>
-      </c>
-      <c r="Y22">
-        <v>1.0394</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD22">
-        <v>7.48</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>66</v>
-      </c>
       <c r="AF22">
-        <v>0.2571</v>
+        <v>0.1773</v>
       </c>
       <c r="AG22">
-        <v>1.1685</v>
+        <v>0.7769</v>
       </c>
       <c r="AH22">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>6.88</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2747,28 +2732,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>-140</v>
+        <v>116</v>
       </c>
       <c r="E23">
-        <v>130</v>
+        <v>-135</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>824962</v>
+        <v>825042</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2780,43 +2765,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2438</v>
+        <v>0.1712</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="P23">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q23">
-        <v>0.2328</v>
+        <v>0.1951</v>
       </c>
       <c r="R23">
-        <v>0.367</v>
+        <v>0.381</v>
       </c>
       <c r="S23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T23">
-        <v>0.182</v>
+        <v>0.2167</v>
       </c>
       <c r="U23">
-        <v>0.1816</v>
+        <v>0.2155</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2191</v>
+        <v>0.2173</v>
       </c>
       <c r="X23">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y23">
-        <v>0.9797</v>
+        <v>0.9878</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2825,22 +2810,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
       <c r="AE23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF23">
-        <v>0.2397</v>
+        <v>0.1803</v>
       </c>
       <c r="AG23">
-        <v>0.8245</v>
+        <v>1.0029</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2848,22 +2833,22 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>5.5</v>
       </c>
       <c r="D24">
-        <v>-120</v>
+        <v>-154</v>
       </c>
       <c r="E24">
-        <v>-104</v>
+        <v>128</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24">
-        <v>823098</v>
+        <v>823259</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
@@ -2881,67 +2866,67 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2462</v>
+        <v>0.2984</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="Q24">
-        <v>0.2881</v>
+        <v>0.3056</v>
       </c>
       <c r="R24">
-        <v>0.371</v>
+        <v>0.351</v>
       </c>
       <c r="S24" t="s">
+        <v>53</v>
+      </c>
+      <c r="T24">
+        <v>0.1828</v>
+      </c>
+      <c r="U24">
+        <v>0.1845</v>
+      </c>
+      <c r="V24">
+        <v>8</v>
+      </c>
+      <c r="W24">
+        <v>0.2161</v>
+      </c>
+      <c r="X24">
+        <v>0.216</v>
+      </c>
+      <c r="Y24">
+        <v>0.9905</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD24">
+        <v>5.56</v>
+      </c>
+      <c r="AE24" t="s">
         <v>47</v>
       </c>
-      <c r="T24">
-        <v>0.2402</v>
-      </c>
-      <c r="U24">
-        <v>0.2195</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.2254</v>
-      </c>
-      <c r="X24">
-        <v>0.2207</v>
-      </c>
-      <c r="Y24">
-        <v>1.0109</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD24">
-        <v>6.57</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>45</v>
-      </c>
       <c r="AF24">
-        <v>0.2618</v>
+        <v>0.3009</v>
       </c>
       <c r="AG24">
-        <v>1.0882</v>
+        <v>0.8462</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>6.57</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2949,28 +2934,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>-114</v>
+        <v>-105</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>823098</v>
+        <v>823259</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2982,43 +2967,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1993</v>
+        <v>0.2098</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="P25">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="Q25">
-        <v>0.1182</v>
+        <v>0.2101</v>
       </c>
       <c r="R25">
-        <v>0.355</v>
+        <v>0.373</v>
       </c>
       <c r="S25" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T25">
-        <v>0.1484</v>
+        <v>0.1979</v>
       </c>
       <c r="U25">
-        <v>0.1505</v>
+        <v>0.2227</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2203</v>
+        <v>0.2371</v>
       </c>
       <c r="X25">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y25">
-        <v>0.9783</v>
+        <v>1.0167</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3027,22 +3012,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.74</v>
+        <v>4.59</v>
       </c>
       <c r="AE25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF25">
-        <v>0.1705</v>
+        <v>0.2099</v>
       </c>
       <c r="AG25">
-        <v>0.6724</v>
+        <v>0.9161</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>2.74</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3050,28 +3035,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>5.5</v>
       </c>
       <c r="D26">
-        <v>-154</v>
+        <v>-105</v>
       </c>
       <c r="E26">
-        <v>128</v>
+        <v>-104</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26">
-        <v>823259</v>
+        <v>824962</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3083,43 +3068,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2984</v>
+        <v>0.2638</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="P26">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="Q26">
-        <v>0.3056</v>
+        <v>0.2458</v>
       </c>
       <c r="R26">
-        <v>0.351</v>
+        <v>0.371</v>
       </c>
       <c r="S26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T26">
-        <v>0.1828</v>
+        <v>0.2579</v>
       </c>
       <c r="U26">
-        <v>0.1845</v>
+        <v>0.2281</v>
       </c>
       <c r="V26">
         <v>8</v>
       </c>
       <c r="W26">
-        <v>0.2161</v>
+        <v>0.2132</v>
       </c>
       <c r="X26">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y26">
-        <v>0.9905</v>
+        <v>1.0394</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3128,22 +3113,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.44</v>
+        <v>7.64</v>
       </c>
       <c r="AE26" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="AF26">
-        <v>0.3009</v>
+        <v>0.2571</v>
       </c>
       <c r="AG26">
-        <v>0.8283</v>
+        <v>1.1936</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM26">
-        <v>5.44</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3151,28 +3136,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-105</v>
+        <v>-140</v>
       </c>
       <c r="E27">
-        <v>-111</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>823259</v>
+        <v>824962</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3184,43 +3169,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2098</v>
+        <v>0.2438</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P27">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="Q27">
-        <v>0.2101</v>
+        <v>0.2328</v>
       </c>
       <c r="R27">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="S27" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T27">
-        <v>0.1979</v>
+        <v>0.182</v>
       </c>
       <c r="U27">
-        <v>0.2227</v>
+        <v>0.1816</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2371</v>
+        <v>0.2191</v>
       </c>
       <c r="X27">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y27">
-        <v>1.0167</v>
+        <v>0.9797</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3229,22 +3214,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="AE27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF27">
-        <v>0.2099</v>
+        <v>0.2397</v>
       </c>
       <c r="AG27">
-        <v>0.8968</v>
+        <v>0.8423</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3252,28 +3237,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28">
+        <v>5.5</v>
+      </c>
+      <c r="D28">
+        <v>-120</v>
+      </c>
+      <c r="E28">
+        <v>-104</v>
+      </c>
+      <c r="F28" t="s">
         <v>88</v>
       </c>
-      <c r="C28">
-        <v>3.5</v>
-      </c>
-      <c r="D28">
-        <v>-140</v>
-      </c>
-      <c r="E28">
-        <v>123</v>
-      </c>
-      <c r="F28" t="s">
-        <v>89</v>
-      </c>
       <c r="G28">
-        <v>823181</v>
+        <v>823098</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3285,43 +3270,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.1573</v>
+        <v>0.2462</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="P28">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>0.2529</v>
+        <v>0.2881</v>
       </c>
       <c r="R28">
-        <v>0.303</v>
+        <v>0.371</v>
       </c>
       <c r="S28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T28">
-        <v>0.3635</v>
+        <v>0.2402</v>
       </c>
       <c r="U28">
-        <v>0.2882</v>
+        <v>0.2195</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2558</v>
+        <v>0.2254</v>
       </c>
       <c r="X28">
-        <v>0.2207</v>
+        <v>0.216</v>
       </c>
       <c r="Y28">
-        <v>1.046</v>
+        <v>1.0109</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3330,22 +3315,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.43</v>
+        <v>6.71</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.1809</v>
+        <v>0.2618</v>
       </c>
       <c r="AG28">
-        <v>1.647</v>
+        <v>1.1116</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>6.43</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3353,28 +3338,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29">
         <v>4.5</v>
       </c>
       <c r="D29">
-        <v>116</v>
+        <v>-114</v>
       </c>
       <c r="E29">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>823181</v>
+        <v>823098</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3386,67 +3371,67 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.1835</v>
+        <v>0.1993</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="P29">
-        <v>4.43</v>
+        <v>4.19</v>
       </c>
       <c r="Q29">
-        <v>0.1473</v>
+        <v>0.1182</v>
       </c>
       <c r="R29">
-        <v>0.392</v>
+        <v>0.355</v>
       </c>
       <c r="S29" t="s">
+        <v>53</v>
+      </c>
+      <c r="T29">
+        <v>0.1484</v>
+      </c>
+      <c r="U29">
+        <v>0.1505</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.2203</v>
+      </c>
+      <c r="X29">
+        <v>0.216</v>
+      </c>
+      <c r="Y29">
+        <v>0.9783</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD29">
+        <v>2.8</v>
+      </c>
+      <c r="AE29" t="s">
         <v>47</v>
       </c>
-      <c r="T29">
-        <v>0.2064</v>
-      </c>
-      <c r="U29">
-        <v>0.2055</v>
-      </c>
-      <c r="V29">
-        <v>7</v>
-      </c>
-      <c r="W29">
-        <v>0.2044</v>
-      </c>
-      <c r="X29">
-        <v>0.2207</v>
-      </c>
-      <c r="Y29">
-        <v>0.9925</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD29">
-        <v>3.67</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>48</v>
-      </c>
       <c r="AF29">
-        <v>0.1693</v>
+        <v>0.1705</v>
       </c>
       <c r="AG29">
-        <v>0.9353</v>
+        <v>0.6869</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.67</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3454,19 +3439,28 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>116</v>
+      </c>
+      <c r="E30">
+        <v>-133</v>
+      </c>
+      <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
       <c r="G30">
-        <v>823585</v>
+        <v>823181</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3475,70 +3469,171 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>0.18</v>
+        <v>0.1835</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="P30">
-        <v>3.97</v>
+        <v>4.43</v>
       </c>
       <c r="Q30">
-        <v>0.1681</v>
+        <v>0.1473</v>
       </c>
       <c r="R30">
-        <v>0.361</v>
+        <v>0.392</v>
       </c>
       <c r="S30" t="s">
+        <v>53</v>
+      </c>
+      <c r="T30">
+        <v>0.2064</v>
+      </c>
+      <c r="U30">
+        <v>0.2055</v>
+      </c>
+      <c r="V30">
+        <v>7</v>
+      </c>
+      <c r="W30">
+        <v>0.2044</v>
+      </c>
+      <c r="X30">
+        <v>0.216</v>
+      </c>
+      <c r="Y30">
+        <v>0.9925</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30">
+        <v>3.74</v>
+      </c>
+      <c r="AE30" t="s">
         <v>47</v>
       </c>
-      <c r="T30">
-        <v>0.2286</v>
-      </c>
-      <c r="U30">
-        <v>0.2264</v>
-      </c>
-      <c r="V30">
-        <v>8</v>
-      </c>
-      <c r="W30">
-        <v>0.2197</v>
-      </c>
-      <c r="X30">
-        <v>0.2207</v>
-      </c>
-      <c r="Y30">
-        <v>1.0023</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD30">
-        <v>4.05</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>48</v>
-      </c>
       <c r="AF30">
-        <v>0.1757</v>
+        <v>0.1693</v>
       </c>
       <c r="AG30">
-        <v>1.036</v>
+        <v>0.9554</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.05</v>
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31">
+        <v>3.5</v>
+      </c>
+      <c r="D31">
+        <v>-140</v>
+      </c>
+      <c r="E31">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31">
+        <v>823181</v>
+      </c>
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>4.8</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>6</v>
+      </c>
+      <c r="M31">
+        <v>0.1573</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>87</v>
+      </c>
+      <c r="P31">
+        <v>4.3</v>
+      </c>
+      <c r="Q31">
+        <v>0.2529</v>
+      </c>
+      <c r="R31">
+        <v>0.303</v>
+      </c>
+      <c r="S31" t="s">
+        <v>53</v>
+      </c>
+      <c r="T31">
+        <v>0.3635</v>
+      </c>
+      <c r="U31">
+        <v>0.2882</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.2558</v>
+      </c>
+      <c r="X31">
+        <v>0.216</v>
+      </c>
+      <c r="Y31">
+        <v>1.046</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31">
+        <v>6.57</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF31">
+        <v>0.1809</v>
+      </c>
+      <c r="AG31">
+        <v>1.6825</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>6.57</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="95">
   <si>
     <t>date</t>
   </si>
@@ -133,6 +133,24 @@
     <t>08/25/2026</t>
   </si>
   <si>
+    <t>Casey Legumina</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
     <t>Payton Tolle</t>
   </si>
   <si>
@@ -142,154 +160,142 @@
     <t>Traditional starter</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
     <t>Tyler Phillips</t>
   </si>
   <si>
-    <t>&lt;6</t>
+    <t>Andrew Alvarez</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Seth Lugo</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Max Scherzer</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
+    <t>Tyler Glasnow</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Anthony Kay</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Brandon Pfaadt</t>
+  </si>
+  <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Gage Jump</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Adrian Houser</t>
   </si>
   <si>
     <t>Jackson Jobe</t>
   </si>
   <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
     <t>Ian Seymour</t>
   </si>
   <si>
-    <t>Andrew Alvarez</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
     <t>Ethan Pecko</t>
   </si>
   <si>
-    <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
-  </si>
-  <si>
-    <t>Seth Lugo</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Max Scherzer</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
     <t>Zach Thornton</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ New York Mets</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>Tyler Glasnow</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Anthony Kay</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>Gavin Williams</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Gage Jump</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>George Kirby</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Adrian Houser</t>
   </si>
 </sst>
 </file>
@@ -670,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -802,74 +808,65 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>6.5</v>
-      </c>
-      <c r="D2">
-        <v>120</v>
-      </c>
-      <c r="E2">
-        <v>-137</v>
-      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823826</v>
+        <v>824233</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.2774</v>
+        <v>0.1799</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="P2">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="Q2">
-        <v>0.3276</v>
+        <v>0.129</v>
       </c>
       <c r="R2">
-        <v>0.367</v>
+        <v>0.134</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2391</v>
+        <v>0.1947</v>
       </c>
       <c r="U2">
-        <v>0.2122</v>
+        <v>0.1919</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2307</v>
+        <v>0.2237</v>
       </c>
       <c r="X2">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y2">
-        <v>0.8824</v>
+        <v>0.906</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -878,22 +875,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.65</v>
+        <v>0.95</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2958</v>
+        <v>0.1731</v>
       </c>
       <c r="AG2">
-        <v>1.1069</v>
+        <v>0.8927</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.65</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -904,25 +901,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
-        <v>-120</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>116</v>
+        <v>-137</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>823826</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -934,43 +931,43 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.182</v>
+        <v>0.2774</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="P3">
-        <v>4.31</v>
+        <v>4.03</v>
       </c>
       <c r="Q3">
-        <v>0.2</v>
+        <v>0.3276</v>
       </c>
       <c r="R3">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1854</v>
+        <v>0.2391</v>
       </c>
       <c r="U3">
-        <v>0.199</v>
+        <v>0.2122</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2139</v>
+        <v>0.2307</v>
       </c>
       <c r="X3">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y3">
-        <v>0.9777</v>
+        <v>0.8824</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -979,22 +976,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.11</v>
+        <v>6.58</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF3">
-        <v>0.188</v>
+        <v>0.2958</v>
       </c>
       <c r="AG3">
-        <v>0.8582</v>
+        <v>1.0966</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.11</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1002,34 +999,76 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>107</v>
+        <v>-120</v>
       </c>
       <c r="E4">
-        <v>-132</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="G4">
+        <v>823826</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="I4">
+        <v>4.6</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
       </c>
       <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
+        <v>0.182</v>
+      </c>
+      <c r="N4">
         <v>5</v>
       </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>4.31</v>
+      </c>
+      <c r="Q4">
+        <v>0.2</v>
+      </c>
+      <c r="R4">
+        <v>0.333</v>
+      </c>
       <c r="S4" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T4">
+        <v>0.1854</v>
+      </c>
+      <c r="U4">
+        <v>0.199</v>
+      </c>
+      <c r="V4">
+        <v>9</v>
+      </c>
+      <c r="W4">
+        <v>0.2139</v>
+      </c>
+      <c r="X4">
+        <v>0.2181</v>
+      </c>
+      <c r="Y4">
+        <v>0.9777</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1037,8 +1076,23 @@
       <c r="AC4" t="s">
         <v>44</v>
       </c>
+      <c r="AD4">
+        <v>3.08</v>
+      </c>
       <c r="AE4" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF4">
+        <v>0.188</v>
+      </c>
+      <c r="AG4">
+        <v>0.8502</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>3.08</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1046,28 +1100,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-122</v>
+        <v>-130</v>
       </c>
       <c r="E5">
-        <v>-106</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5">
-        <v>824233</v>
+        <v>822693</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1076,46 +1130,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>0.2922</v>
+        <v>0.2183</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P5">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="Q5">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="R5">
-        <v>0.357</v>
+        <v>0.351</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1947</v>
+        <v>0.2643</v>
       </c>
       <c r="U5">
-        <v>0.1919</v>
+        <v>0.2432</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2277</v>
+        <v>0.2478</v>
       </c>
       <c r="X5">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y5">
-        <v>0.9633</v>
+        <v>1.0972</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1124,22 +1178,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="AE5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.3069</v>
+        <v>0.2002</v>
       </c>
       <c r="AG5">
-        <v>0.9011</v>
+        <v>1.212</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1147,28 +1201,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-130</v>
+        <v>-135</v>
       </c>
       <c r="E6">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>822693</v>
+        <v>823505</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1177,46 +1231,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2183</v>
+        <v>0.228</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P6">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="Q6">
-        <v>0.1667</v>
+        <v>0.2451</v>
       </c>
       <c r="R6">
-        <v>0.351</v>
+        <v>0.338</v>
       </c>
       <c r="S6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2285</v>
+        <v>0.2167</v>
       </c>
       <c r="U6">
-        <v>0.2221</v>
+        <v>0.2115</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2478</v>
+        <v>0.2189</v>
       </c>
       <c r="X6">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y6">
-        <v>1.0329</v>
+        <v>0.9612</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1225,22 +1279,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.49</v>
+        <v>4.95</v>
       </c>
       <c r="AE6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2002</v>
+        <v>0.2338</v>
       </c>
       <c r="AG6">
-        <v>1.0579</v>
+        <v>0.9937</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.49</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1248,34 +1302,76 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>-130</v>
       </c>
       <c r="E7">
-        <v>-143</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>822773</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="I7">
+        <v>5.6</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
+      <c r="M7">
+        <v>0.1793</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>120</v>
+      </c>
+      <c r="P7">
+        <v>4.26</v>
+      </c>
+      <c r="Q7">
+        <v>0.1417</v>
+      </c>
+      <c r="R7">
+        <v>0.375</v>
+      </c>
       <c r="S7" t="s">
-        <v>44</v>
-      </c>
-      <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T7">
+        <v>0.2005</v>
+      </c>
+      <c r="U7">
+        <v>0.1876</v>
+      </c>
+      <c r="V7">
+        <v>9</v>
+      </c>
+      <c r="W7">
+        <v>0.189</v>
+      </c>
+      <c r="X7">
+        <v>0.2181</v>
+      </c>
+      <c r="Y7">
+        <v>0.9732</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1283,8 +1379,23 @@
       <c r="AC7" t="s">
         <v>44</v>
       </c>
+      <c r="AD7">
+        <v>3.52</v>
+      </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF7">
+        <v>0.1652</v>
+      </c>
+      <c r="AG7">
+        <v>0.9194</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>3.52</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1292,28 +1403,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>3.5</v>
+      </c>
+      <c r="D8">
+        <v>-140</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8" t="s">
         <v>56</v>
       </c>
-      <c r="C8">
-        <v>4.5</v>
-      </c>
-      <c r="D8">
-        <v>-135</v>
-      </c>
-      <c r="E8">
-        <v>119</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
       <c r="G8">
-        <v>823505</v>
+        <v>822773</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I8">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1325,43 +1436,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.228</v>
+        <v>0.1584</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="Q8">
-        <v>0.2451</v>
+        <v>0.18</v>
       </c>
       <c r="R8">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="S8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2188</v>
+        <v>0.1732</v>
       </c>
       <c r="U8">
-        <v>0.2121</v>
+        <v>0.1849</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2189</v>
+        <v>0.208</v>
       </c>
       <c r="X8">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y8">
-        <v>0.996</v>
+        <v>0.8979</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1370,22 +1481,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.23</v>
+        <v>2.17</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2338</v>
+        <v>0.1656</v>
       </c>
       <c r="AG8">
-        <v>1.0128</v>
+        <v>0.7942</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.23</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1393,28 +1504,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-130</v>
+        <v>-114</v>
       </c>
       <c r="E9">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>822773</v>
+        <v>823585</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1426,43 +1537,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.1793</v>
+        <v>0.3035</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="P9">
-        <v>4.26</v>
+        <v>4.09</v>
       </c>
       <c r="Q9">
-        <v>0.1417</v>
+        <v>0.2796</v>
       </c>
       <c r="R9">
-        <v>0.375</v>
+        <v>0.317</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2005</v>
+        <v>0.1933</v>
       </c>
       <c r="U9">
-        <v>0.1876</v>
+        <v>0.2049</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.189</v>
+        <v>0.2322</v>
       </c>
       <c r="X9">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y9">
-        <v>0.9732</v>
+        <v>0.9313</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1471,22 +1582,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.55</v>
+        <v>4.91</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1652</v>
+        <v>0.2959</v>
       </c>
       <c r="AG9">
-        <v>0.9281</v>
+        <v>0.8863</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.55</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1494,28 +1605,19 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10">
-        <v>3.5</v>
-      </c>
-      <c r="D10">
-        <v>-140</v>
-      </c>
-      <c r="E10">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>822773</v>
+        <v>823585</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1524,46 +1626,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.1584</v>
+        <v>0.18</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="P10">
-        <v>4.49</v>
+        <v>3.97</v>
       </c>
       <c r="Q10">
-        <v>0.18</v>
+        <v>0.1681</v>
       </c>
       <c r="R10">
-        <v>0.333</v>
+        <v>0.361</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1732</v>
+        <v>0.2334</v>
       </c>
       <c r="U10">
-        <v>0.1849</v>
+        <v>0.2268</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.208</v>
+        <v>0.2197</v>
       </c>
       <c r="X10">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y10">
-        <v>0.8979</v>
+        <v>0.9845</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1572,22 +1674,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.19</v>
+        <v>4.11</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1656</v>
+        <v>0.1757</v>
       </c>
       <c r="AG10">
-        <v>0.8017</v>
+        <v>1.0702</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.19</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1595,34 +1697,76 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>-140</v>
+        <v>-160</v>
       </c>
       <c r="E11">
         <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>824881</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="I11">
+        <v>5.7</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
+      <c r="M11">
+        <v>0.3311</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>101</v>
+      </c>
+      <c r="P11">
+        <v>3.73</v>
+      </c>
+      <c r="Q11">
+        <v>0.3366</v>
+      </c>
+      <c r="R11">
+        <v>0.336</v>
+      </c>
       <c r="S11" t="s">
-        <v>44</v>
-      </c>
-      <c r="V11" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T11">
+        <v>0.2367</v>
+      </c>
+      <c r="U11">
+        <v>0.2268</v>
+      </c>
+      <c r="V11">
+        <v>9</v>
+      </c>
+      <c r="W11">
+        <v>0.2195</v>
+      </c>
+      <c r="X11">
+        <v>0.2181</v>
+      </c>
+      <c r="Y11">
+        <v>0.9769</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1630,8 +1774,23 @@
       <c r="AC11" t="s">
         <v>44</v>
       </c>
+      <c r="AD11">
+        <v>7.46</v>
+      </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>64</v>
+      </c>
+      <c r="AF11">
+        <v>0.3329</v>
+      </c>
+      <c r="AG11">
+        <v>1.0852</v>
+      </c>
+      <c r="AH11">
+        <v>-0.6</v>
+      </c>
+      <c r="AM11">
+        <v>6.86</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1639,28 +1798,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>128</v>
+      </c>
+      <c r="E12">
+        <v>-152</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-      <c r="D12">
-        <v>-114</v>
-      </c>
-      <c r="E12">
-        <v>120</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
       <c r="G12">
-        <v>823585</v>
+        <v>824881</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1672,43 +1831,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.3035</v>
+        <v>0.1952</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="P12">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="Q12">
-        <v>0.2796</v>
+        <v>0.1885</v>
       </c>
       <c r="R12">
-        <v>0.317</v>
+        <v>0.379</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1933</v>
+        <v>0.2135</v>
       </c>
       <c r="U12">
-        <v>0.2049</v>
+        <v>0.1988</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2322</v>
+        <v>0.2072</v>
       </c>
       <c r="X12">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y12">
-        <v>0.9313</v>
+        <v>0.9474</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1717,22 +1876,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.96</v>
+        <v>4.31</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2959</v>
+        <v>0.1926</v>
       </c>
       <c r="AG12">
-        <v>0.8947</v>
+        <v>0.979</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.96</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1740,19 +1899,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="C13">
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <v>-108</v>
+      </c>
+      <c r="E13">
+        <v>-105</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G13">
-        <v>823585</v>
+        <v>824556</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1761,46 +1929,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>0.18</v>
+        <v>0.3031</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="P13">
-        <v>3.97</v>
+        <v>4.09</v>
       </c>
       <c r="Q13">
-        <v>0.1681</v>
+        <v>0.3085</v>
       </c>
       <c r="R13">
-        <v>0.361</v>
+        <v>0.32</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2334</v>
+        <v>0.2481</v>
       </c>
       <c r="U13">
-        <v>0.2268</v>
+        <v>0.2564</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2197</v>
+        <v>0.2377</v>
       </c>
       <c r="X13">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y13">
-        <v>0.9845</v>
+        <v>1.0634</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1809,22 +1977,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.15</v>
+        <v>7.96</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF13">
-        <v>0.1757</v>
+        <v>0.3048</v>
       </c>
       <c r="AG13">
-        <v>1.0803</v>
+        <v>1.1377</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM13">
-        <v>4.15</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1832,28 +2000,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D14">
-        <v>-160</v>
+        <v>-120</v>
       </c>
       <c r="E14">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
-        <v>824881</v>
+        <v>824556</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1865,43 +2033,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.3311</v>
+        <v>0.1841</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="P14">
-        <v>3.73</v>
+        <v>4.44</v>
       </c>
       <c r="Q14">
-        <v>0.3366</v>
+        <v>0.1983</v>
       </c>
       <c r="R14">
-        <v>0.336</v>
+        <v>0.377</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="T14">
-        <v>0.2367</v>
+        <v>0.2379</v>
       </c>
       <c r="U14">
-        <v>0.2268</v>
+        <v>0.238</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.2195</v>
+        <v>0.2428</v>
       </c>
       <c r="X14">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y14">
-        <v>0.9769</v>
+        <v>1.0234</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1910,22 +2078,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>7.53</v>
+        <v>4.71</v>
       </c>
       <c r="AE14" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.3329</v>
+        <v>0.1895</v>
       </c>
       <c r="AG14">
-        <v>1.0954</v>
+        <v>1.0911</v>
       </c>
       <c r="AH14">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>6.93</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1933,28 +2101,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D15">
-        <v>128</v>
+        <v>-120</v>
       </c>
       <c r="E15">
-        <v>-152</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G15">
-        <v>824881</v>
+        <v>823016</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1966,43 +2134,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1952</v>
+        <v>0.1489</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="P15">
-        <v>4.21</v>
+        <v>4.59</v>
       </c>
       <c r="Q15">
-        <v>0.1885</v>
+        <v>0.1455</v>
       </c>
       <c r="R15">
-        <v>0.379</v>
+        <v>0.355</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2135</v>
+        <v>0.1757</v>
       </c>
       <c r="U15">
-        <v>0.1988</v>
+        <v>0.1924</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.2072</v>
+        <v>0.2142</v>
       </c>
       <c r="X15">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y15">
-        <v>0.9474</v>
+        <v>0.9745</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2011,22 +2179,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.35</v>
+        <v>2.53</v>
       </c>
       <c r="AE15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1926</v>
+        <v>0.1477</v>
       </c>
       <c r="AG15">
-        <v>0.9882</v>
+        <v>0.8057</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.35</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2034,28 +2202,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-      <c r="D16">
-        <v>-108</v>
-      </c>
-      <c r="E16">
-        <v>-105</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16">
-        <v>824556</v>
+        <v>823016</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I16">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2064,46 +2223,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>0.3031</v>
+        <v>0.2311</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="P16">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="Q16">
-        <v>0.3085</v>
+        <v>0.2885</v>
       </c>
       <c r="R16">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="S16" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2313</v>
+        <v>0.2457</v>
       </c>
       <c r="U16">
-        <v>0.2516</v>
+        <v>0.235</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2377</v>
+        <v>0.2573</v>
       </c>
       <c r="X16">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y16">
-        <v>1.0329</v>
+        <v>1.0581</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2112,22 +2271,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>7.28</v>
+        <v>6.47</v>
       </c>
       <c r="AE16" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AF16">
-        <v>0.3048</v>
+        <v>0.2507</v>
       </c>
       <c r="AG16">
-        <v>1.0707</v>
+        <v>1.1266</v>
       </c>
       <c r="AH16">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.68</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2135,76 +2294,76 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D17">
-        <v>-120</v>
+        <v>116</v>
       </c>
       <c r="E17">
-        <v>105</v>
+        <v>-138</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17">
-        <v>824556</v>
+        <v>823989</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I17">
+        <v>5.9</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>5</v>
       </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>6</v>
-      </c>
       <c r="M17">
-        <v>0.1841</v>
+        <v>0.3237</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P17">
-        <v>4.44</v>
+        <v>4.02</v>
       </c>
       <c r="Q17">
-        <v>0.1983</v>
+        <v>0.3982</v>
       </c>
       <c r="R17">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S17" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T17">
-        <v>0.2379</v>
+        <v>0.2472</v>
       </c>
       <c r="U17">
-        <v>0.238</v>
+        <v>0.2397</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2428</v>
+        <v>0.2511</v>
       </c>
       <c r="X17">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y17">
-        <v>1.0234</v>
+        <v>1.0421</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2213,22 +2372,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.75</v>
+        <v>9.89</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF17">
-        <v>0.1895</v>
+        <v>0.3506</v>
       </c>
       <c r="AG17">
-        <v>1.1014</v>
+        <v>1.1333</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM17">
-        <v>4.75</v>
+        <v>9.29</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2236,28 +2395,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-120</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>104</v>
+        <v>-155</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
-        <v>823016</v>
+        <v>823989</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I18">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2266,46 +2425,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>0.1489</v>
+        <v>0.2276</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="P18">
-        <v>4.59</v>
+        <v>4.25</v>
       </c>
       <c r="Q18">
-        <v>0.1455</v>
+        <v>0.2574</v>
       </c>
       <c r="R18">
-        <v>0.355</v>
+        <v>0.336</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="T18">
-        <v>0.1757</v>
+        <v>0.2037</v>
       </c>
       <c r="U18">
-        <v>0.1924</v>
+        <v>0.1828</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2142</v>
+        <v>0.2107</v>
       </c>
       <c r="X18">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y18">
-        <v>0.9745</v>
+        <v>0.9595</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2314,22 +2473,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.55</v>
+        <v>4.78</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.1477</v>
+        <v>0.2376</v>
       </c>
       <c r="AG18">
-        <v>0.8133</v>
+        <v>0.934</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>2.55</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2337,19 +2496,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="C19">
+        <v>3.5</v>
+      </c>
+      <c r="D19">
+        <v>107</v>
+      </c>
+      <c r="E19">
+        <v>-132</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>823016</v>
+        <v>825042</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2358,46 +2526,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2311</v>
+        <v>0.1799</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="P19">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q19">
-        <v>0.2885</v>
+        <v>0.1727</v>
       </c>
       <c r="R19">
-        <v>0.342</v>
+        <v>0.355</v>
       </c>
       <c r="S19" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T19">
-        <v>0.2528</v>
+        <v>0.1678</v>
       </c>
       <c r="U19">
-        <v>0.2394</v>
+        <v>0.1685</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2573</v>
+        <v>0.1976</v>
       </c>
       <c r="X19">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y19">
-        <v>1.0429</v>
+        <v>0.9284</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2406,22 +2574,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.62</v>
+        <v>2.94</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2507</v>
+        <v>0.1773</v>
       </c>
       <c r="AG19">
-        <v>1.1701</v>
+        <v>0.7696</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>6.62</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2429,25 +2597,25 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
         <v>116</v>
       </c>
       <c r="E20">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20">
-        <v>823989</v>
+        <v>825042</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I20">
         <v>5.9</v>
@@ -2459,46 +2627,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>0.3237</v>
+        <v>0.1712</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="P20">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
-        <v>0.3982</v>
+        <v>0.1951</v>
       </c>
       <c r="R20">
-        <v>0.361</v>
+        <v>0.381</v>
       </c>
       <c r="S20" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T20">
-        <v>0.2472</v>
+        <v>0.2167</v>
       </c>
       <c r="U20">
-        <v>0.2397</v>
+        <v>0.2155</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2511</v>
+        <v>0.2173</v>
       </c>
       <c r="X20">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y20">
-        <v>1.0421</v>
+        <v>0.9878</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2507,22 +2675,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>9.98</v>
+        <v>4.3</v>
       </c>
       <c r="AE20" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.3506</v>
+        <v>0.1803</v>
       </c>
       <c r="AG20">
-        <v>1.144</v>
+        <v>0.9935</v>
       </c>
       <c r="AH20">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>9.38</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2530,25 +2698,25 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>130</v>
+        <v>-154</v>
       </c>
       <c r="E21">
-        <v>-155</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
-        <v>823989</v>
+        <v>823259</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I21">
         <v>5.3</v>
@@ -2560,46 +2728,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2276</v>
+        <v>0.2984</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="Q21">
-        <v>0.2574</v>
+        <v>0.3056</v>
       </c>
       <c r="R21">
-        <v>0.336</v>
+        <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T21">
-        <v>0.2037</v>
+        <v>0.1828</v>
       </c>
       <c r="U21">
-        <v>0.1828</v>
+        <v>0.1845</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2107</v>
+        <v>0.2161</v>
       </c>
       <c r="X21">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y21">
-        <v>0.9595</v>
+        <v>0.9905</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2608,22 +2776,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.83</v>
+        <v>5.51</v>
       </c>
       <c r="AE21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2376</v>
+        <v>0.3009</v>
       </c>
       <c r="AG21">
-        <v>0.9428</v>
+        <v>0.8383</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.83</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2631,25 +2799,25 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C22">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>107</v>
+        <v>-105</v>
       </c>
       <c r="E22">
-        <v>-132</v>
+        <v>-111</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
-        <v>825042</v>
+        <v>823259</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I22">
         <v>5.7</v>
@@ -2664,43 +2832,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1799</v>
+        <v>0.2098</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="P22">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="Q22">
-        <v>0.1727</v>
+        <v>0.2101</v>
       </c>
       <c r="R22">
-        <v>0.355</v>
+        <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T22">
-        <v>0.1678</v>
+        <v>0.1979</v>
       </c>
       <c r="U22">
-        <v>0.1685</v>
+        <v>0.2227</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.1976</v>
+        <v>0.2371</v>
       </c>
       <c r="X22">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y22">
-        <v>0.9284</v>
+        <v>1.0167</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2709,22 +2877,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.96</v>
+        <v>4.54</v>
       </c>
       <c r="AE22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.1773</v>
+        <v>0.2099</v>
       </c>
       <c r="AG22">
-        <v>0.7769</v>
+        <v>0.9075</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.96</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2732,28 +2900,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>116</v>
+        <v>-105</v>
       </c>
       <c r="E23">
-        <v>-135</v>
+        <v>-104</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G23">
-        <v>825042</v>
+        <v>824962</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I23">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2765,43 +2933,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1712</v>
+        <v>0.2638</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="P23">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="Q23">
-        <v>0.1951</v>
+        <v>0.2458</v>
       </c>
       <c r="R23">
-        <v>0.381</v>
+        <v>0.371</v>
       </c>
       <c r="S23" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T23">
-        <v>0.2167</v>
+        <v>0.2579</v>
       </c>
       <c r="U23">
-        <v>0.2155</v>
+        <v>0.2281</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>0.2173</v>
+        <v>0.2132</v>
       </c>
       <c r="X23">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y23">
-        <v>0.9878</v>
+        <v>1.0394</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2810,22 +2978,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.34</v>
+        <v>7.57</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF23">
-        <v>0.1803</v>
+        <v>0.2571</v>
       </c>
       <c r="AG23">
-        <v>1.0029</v>
+        <v>1.1825</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM23">
-        <v>4.34</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2833,28 +3001,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-154</v>
+        <v>-140</v>
       </c>
       <c r="E24">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>823259</v>
+        <v>824962</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I24">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2866,43 +3034,43 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2984</v>
+        <v>0.2438</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="P24">
-        <v>4.12</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
-        <v>0.3056</v>
+        <v>0.2328</v>
       </c>
       <c r="R24">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="S24" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.1828</v>
+        <v>0.1996</v>
       </c>
       <c r="U24">
-        <v>0.1845</v>
+        <v>0.1929</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2161</v>
+        <v>0.2191</v>
       </c>
       <c r="X24">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y24">
-        <v>0.9905</v>
+        <v>0.9649</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2911,22 +3079,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.56</v>
+        <v>4.78</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.3009</v>
+        <v>0.2397</v>
       </c>
       <c r="AG24">
-        <v>0.8462</v>
+        <v>0.9151</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.56</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2934,28 +3102,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25">
         <v>5.5</v>
       </c>
       <c r="D25">
-        <v>-105</v>
+        <v>-120</v>
       </c>
       <c r="E25">
-        <v>-111</v>
+        <v>-104</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25">
-        <v>823259</v>
+        <v>823098</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I25">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2967,43 +3135,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2098</v>
+        <v>0.2462</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P25">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>0.2101</v>
+        <v>0.2881</v>
       </c>
       <c r="R25">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="S25" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T25">
-        <v>0.1979</v>
+        <v>0.2402</v>
       </c>
       <c r="U25">
-        <v>0.2227</v>
+        <v>0.2195</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2371</v>
+        <v>0.2254</v>
       </c>
       <c r="X25">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y25">
-        <v>1.0167</v>
+        <v>1.0109</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3012,22 +3180,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.59</v>
+        <v>6.65</v>
       </c>
       <c r="AE25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF25">
-        <v>0.2099</v>
+        <v>0.2618</v>
       </c>
       <c r="AG25">
-        <v>0.9161</v>
+        <v>1.1012</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.59</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3035,28 +3203,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>-105</v>
+        <v>-114</v>
       </c>
       <c r="E26">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G26">
-        <v>824962</v>
+        <v>823098</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3068,43 +3236,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2638</v>
+        <v>0.1993</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="Q26">
-        <v>0.2458</v>
+        <v>0.1182</v>
       </c>
       <c r="R26">
-        <v>0.371</v>
+        <v>0.355</v>
       </c>
       <c r="S26" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T26">
-        <v>0.2579</v>
+        <v>0.1484</v>
       </c>
       <c r="U26">
-        <v>0.2281</v>
+        <v>0.1505</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2132</v>
+        <v>0.2203</v>
       </c>
       <c r="X26">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y26">
-        <v>1.0394</v>
+        <v>0.9783</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3113,22 +3281,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>7.64</v>
+        <v>2.78</v>
       </c>
       <c r="AE26" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.2571</v>
+        <v>0.1705</v>
       </c>
       <c r="AG26">
-        <v>1.1936</v>
+        <v>0.6805</v>
       </c>
       <c r="AH26">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>7.04</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3136,28 +3304,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-140</v>
+        <v>116</v>
       </c>
       <c r="E27">
-        <v>130</v>
+        <v>-133</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G27">
-        <v>824962</v>
+        <v>823181</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3169,43 +3337,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2438</v>
+        <v>0.1835</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="P27">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="Q27">
-        <v>0.2328</v>
+        <v>0.1473</v>
       </c>
       <c r="R27">
-        <v>0.367</v>
+        <v>0.392</v>
       </c>
       <c r="S27" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T27">
-        <v>0.182</v>
+        <v>0.2064</v>
       </c>
       <c r="U27">
-        <v>0.1816</v>
+        <v>0.2055</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>0.2191</v>
+        <v>0.2044</v>
       </c>
       <c r="X27">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y27">
-        <v>0.9797</v>
+        <v>0.9925</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3214,22 +3382,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.46</v>
+        <v>3.71</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.2397</v>
+        <v>0.1693</v>
       </c>
       <c r="AG27">
-        <v>0.8423</v>
+        <v>0.9465</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>4.46</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3237,28 +3405,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D28">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="E28">
-        <v>-104</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G28">
-        <v>823098</v>
+        <v>823181</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I28">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3270,43 +3438,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2462</v>
+        <v>0.1573</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Q28">
-        <v>0.2881</v>
+        <v>0.2529</v>
       </c>
       <c r="R28">
-        <v>0.371</v>
+        <v>0.303</v>
       </c>
       <c r="S28" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="T28">
-        <v>0.2402</v>
+        <v>0.3635</v>
       </c>
       <c r="U28">
-        <v>0.2195</v>
+        <v>0.2882</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2254</v>
+        <v>0.2558</v>
       </c>
       <c r="X28">
-        <v>0.216</v>
+        <v>0.2181</v>
       </c>
       <c r="Y28">
-        <v>1.0109</v>
+        <v>1.046</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3315,22 +3483,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.71</v>
+        <v>6.51</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF28">
-        <v>0.2618</v>
+        <v>0.1809</v>
       </c>
       <c r="AG28">
-        <v>1.1116</v>
+        <v>1.6668</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>6.71</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3338,76 +3506,34 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C29">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D29">
-        <v>-114</v>
+        <v>107</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>-132</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29">
-        <v>823098</v>
+        <v>41</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29">
-        <v>5.8</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L29">
-        <v>6</v>
-      </c>
-      <c r="M29">
-        <v>0.1993</v>
-      </c>
-      <c r="N29">
         <v>5</v>
       </c>
-      <c r="O29">
-        <v>110</v>
-      </c>
-      <c r="P29">
-        <v>4.19</v>
-      </c>
-      <c r="Q29">
-        <v>0.1182</v>
-      </c>
-      <c r="R29">
-        <v>0.355</v>
-      </c>
       <c r="S29" t="s">
-        <v>53</v>
-      </c>
-      <c r="T29">
-        <v>0.1484</v>
-      </c>
-      <c r="U29">
-        <v>0.1505</v>
-      </c>
-      <c r="V29">
-        <v>9</v>
-      </c>
-      <c r="W29">
-        <v>0.2203</v>
-      </c>
-      <c r="X29">
-        <v>0.216</v>
-      </c>
-      <c r="Y29">
-        <v>0.9783</v>
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>44</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3415,23 +3541,8 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
-      <c r="AD29">
-        <v>2.8</v>
-      </c>
       <c r="AE29" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF29">
-        <v>0.1705</v>
-      </c>
-      <c r="AG29">
-        <v>0.6869</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>2.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3439,28 +3550,28 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C30">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D30">
-        <v>116</v>
+        <v>-122</v>
       </c>
       <c r="E30">
-        <v>-133</v>
+        <v>-106</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G30">
-        <v>823181</v>
+        <v>824233</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I30">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3469,46 +3580,46 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>0.1835</v>
+        <v>0.2922</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P30">
-        <v>4.43</v>
+        <v>4.15</v>
       </c>
       <c r="Q30">
-        <v>0.1473</v>
+        <v>0.3333</v>
       </c>
       <c r="R30">
-        <v>0.392</v>
+        <v>0.357</v>
       </c>
       <c r="S30" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2064</v>
+        <v>0.1947</v>
       </c>
       <c r="U30">
-        <v>0.2055</v>
+        <v>0.1919</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2044</v>
+        <v>0.2277</v>
       </c>
       <c r="X30">
         <v>0.216</v>
       </c>
       <c r="Y30">
-        <v>0.9925</v>
+        <v>0.9633</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3517,22 +3628,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="AE30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.1693</v>
+        <v>0.3069</v>
       </c>
       <c r="AG30">
-        <v>0.9554</v>
+        <v>0.9011</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3540,76 +3651,34 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D31">
-        <v>-140</v>
+        <v>124</v>
       </c>
       <c r="E31">
-        <v>123</v>
+        <v>-143</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31">
-        <v>823181</v>
+        <v>54</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31">
-        <v>4.8</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
-      <c r="M31">
-        <v>0.1573</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>87</v>
-      </c>
-      <c r="P31">
-        <v>4.3</v>
-      </c>
-      <c r="Q31">
-        <v>0.2529</v>
-      </c>
-      <c r="R31">
-        <v>0.303</v>
-      </c>
       <c r="S31" t="s">
-        <v>53</v>
-      </c>
-      <c r="T31">
-        <v>0.3635</v>
-      </c>
-      <c r="U31">
-        <v>0.2882</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2558</v>
-      </c>
-      <c r="X31">
-        <v>0.216</v>
-      </c>
-      <c r="Y31">
-        <v>1.046</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3617,23 +3686,52 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>6.57</v>
-      </c>
       <c r="AE31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF31">
-        <v>0.1809</v>
-      </c>
-      <c r="AG31">
-        <v>1.6825</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>6.57</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32">
+        <v>3.5</v>
+      </c>
+      <c r="D32">
+        <v>-140</v>
+      </c>
+      <c r="E32">
+        <v>130</v>
+      </c>
+      <c r="F32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" t="s">
+        <v>44</v>
+      </c>
+      <c r="L32">
+        <v>6</v>
+      </c>
+      <c r="S32" t="s">
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -220,25 +220,25 @@
     <t>Anthony Kay</t>
   </si>
   <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>Gavin Williams</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
   </si>
   <si>
     <t>Clay Holmes</t>
@@ -863,7 +863,7 @@
         <v>0.2237</v>
       </c>
       <c r="X2">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y2">
         <v>0.906</v>
@@ -884,7 +884,7 @@
         <v>0.1731</v>
       </c>
       <c r="AG2">
-        <v>0.8927</v>
+        <v>0.8967</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>0.2307</v>
       </c>
       <c r="X3">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y3">
         <v>0.8824</v>
@@ -976,7 +976,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>6.58</v>
+        <v>6.61</v>
       </c>
       <c r="AE3" t="s">
         <v>49</v>
@@ -985,13 +985,13 @@
         <v>0.2958</v>
       </c>
       <c r="AG3">
-        <v>1.0966</v>
+        <v>1.1015</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>6.58</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1065,7 +1065,7 @@
         <v>0.2139</v>
       </c>
       <c r="X4">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y4">
         <v>0.9777</v>
@@ -1077,7 +1077,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1086,13 +1086,13 @@
         <v>0.188</v>
       </c>
       <c r="AG4">
-        <v>0.8502</v>
+        <v>0.854</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1166,7 +1166,7 @@
         <v>0.2478</v>
       </c>
       <c r="X5">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y5">
         <v>1.0972</v>
@@ -1178,7 +1178,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1187,13 +1187,13 @@
         <v>0.2002</v>
       </c>
       <c r="AG5">
-        <v>1.212</v>
+        <v>1.2174</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1267,7 +1267,7 @@
         <v>0.2189</v>
       </c>
       <c r="X6">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y6">
         <v>0.9612</v>
@@ -1279,7 +1279,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1288,13 +1288,13 @@
         <v>0.2338</v>
       </c>
       <c r="AG6">
-        <v>0.9937</v>
+        <v>0.9982</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1368,7 +1368,7 @@
         <v>0.189</v>
       </c>
       <c r="X7">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y7">
         <v>0.9732</v>
@@ -1380,7 +1380,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1389,13 +1389,13 @@
         <v>0.1652</v>
       </c>
       <c r="AG7">
-        <v>0.9194</v>
+        <v>0.9235</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1469,7 +1469,7 @@
         <v>0.208</v>
       </c>
       <c r="X8">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y8">
         <v>0.8979</v>
@@ -1481,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1490,13 +1490,13 @@
         <v>0.1656</v>
       </c>
       <c r="AG8">
-        <v>0.7942</v>
+        <v>0.7978</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1570,7 +1570,7 @@
         <v>0.2322</v>
       </c>
       <c r="X9">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y9">
         <v>0.9313</v>
@@ -1582,7 +1582,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1591,13 +1591,13 @@
         <v>0.2959</v>
       </c>
       <c r="AG9">
-        <v>0.8863</v>
+        <v>0.8903</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1662,7 +1662,7 @@
         <v>0.2197</v>
       </c>
       <c r="X10">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y10">
         <v>0.9845</v>
@@ -1674,7 +1674,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1683,13 +1683,13 @@
         <v>0.1757</v>
       </c>
       <c r="AG10">
-        <v>1.0702</v>
+        <v>1.075</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1763,7 +1763,7 @@
         <v>0.2195</v>
       </c>
       <c r="X11">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y11">
         <v>0.9769</v>
@@ -1775,7 +1775,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.46</v>
+        <v>7.5</v>
       </c>
       <c r="AE11" t="s">
         <v>64</v>
@@ -1784,13 +1784,13 @@
         <v>0.3329</v>
       </c>
       <c r="AG11">
-        <v>1.0852</v>
+        <v>1.09</v>
       </c>
       <c r="AH11">
         <v>-0.6</v>
       </c>
       <c r="AM11">
-        <v>6.86</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1864,7 +1864,7 @@
         <v>0.2072</v>
       </c>
       <c r="X12">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y12">
         <v>0.9474</v>
@@ -1876,7 +1876,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1885,13 +1885,13 @@
         <v>0.1926</v>
       </c>
       <c r="AG12">
-        <v>0.979</v>
+        <v>0.9834</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1965,7 +1965,7 @@
         <v>0.2377</v>
       </c>
       <c r="X13">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y13">
         <v>1.0634</v>
@@ -1977,7 +1977,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.96</v>
+        <v>7.99</v>
       </c>
       <c r="AE13" t="s">
         <v>64</v>
@@ -1986,13 +1986,13 @@
         <v>0.3048</v>
       </c>
       <c r="AG13">
-        <v>1.1377</v>
+        <v>1.1427</v>
       </c>
       <c r="AH13">
         <v>-0.6</v>
       </c>
       <c r="AM13">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2051,25 +2051,25 @@
         <v>0.377</v>
       </c>
       <c r="S14" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2379</v>
+        <v>0.2569</v>
       </c>
       <c r="U14">
-        <v>0.238</v>
+        <v>0.234</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>0.2428</v>
       </c>
       <c r="X14">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y14">
-        <v>1.0234</v>
+        <v>1.046</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2078,7 +2078,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.71</v>
+        <v>5.22</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2087,13 +2087,13 @@
         <v>0.1895</v>
       </c>
       <c r="AG14">
-        <v>1.0911</v>
+        <v>1.1834</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.71</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2101,7 +2101,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>3.5</v>
@@ -2113,7 +2113,7 @@
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>823016</v>
@@ -2167,7 +2167,7 @@
         <v>0.2142</v>
       </c>
       <c r="X15">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y15">
         <v>0.9745</v>
@@ -2179,7 +2179,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2188,13 +2188,13 @@
         <v>0.1477</v>
       </c>
       <c r="AG15">
-        <v>0.8057</v>
+        <v>0.8093</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2202,10 +2202,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>823016</v>
@@ -2259,7 +2259,7 @@
         <v>0.2573</v>
       </c>
       <c r="X16">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y16">
         <v>1.0581</v>
@@ -2271,7 +2271,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="s">
         <v>49</v>
@@ -2280,13 +2280,13 @@
         <v>0.2507</v>
       </c>
       <c r="AG16">
-        <v>1.1266</v>
+        <v>1.1316</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2294,7 +2294,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>8.5</v>
@@ -2306,7 +2306,7 @@
         <v>-138</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>823989</v>
@@ -2345,13 +2345,13 @@
         <v>0.361</v>
       </c>
       <c r="S17" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2472</v>
+        <v>0.278</v>
       </c>
       <c r="U17">
-        <v>0.2397</v>
+        <v>0.2646</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2360,10 +2360,10 @@
         <v>0.2511</v>
       </c>
       <c r="X17">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y17">
-        <v>1.0421</v>
+        <v>1.0831</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2372,7 +2372,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>9.89</v>
+        <v>11.61</v>
       </c>
       <c r="AE17" t="s">
         <v>64</v>
@@ -2381,13 +2381,13 @@
         <v>0.3506</v>
       </c>
       <c r="AG17">
-        <v>1.1333</v>
+        <v>1.2804</v>
       </c>
       <c r="AH17">
         <v>-0.6</v>
       </c>
       <c r="AM17">
-        <v>9.29</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2395,7 +2395,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2407,7 +2407,7 @@
         <v>-155</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>823989</v>
@@ -2446,7 +2446,7 @@
         <v>0.336</v>
       </c>
       <c r="S18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T18">
         <v>0.2037</v>
@@ -2461,7 +2461,7 @@
         <v>0.2107</v>
       </c>
       <c r="X18">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y18">
         <v>0.9595</v>
@@ -2473,7 +2473,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2482,13 +2482,13 @@
         <v>0.2376</v>
       </c>
       <c r="AG18">
-        <v>0.934</v>
+        <v>0.9382</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2547,7 +2547,7 @@
         <v>0.355</v>
       </c>
       <c r="S19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T19">
         <v>0.1678</v>
@@ -2562,7 +2562,7 @@
         <v>0.1976</v>
       </c>
       <c r="X19">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y19">
         <v>0.9284</v>
@@ -2574,7 +2574,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2583,13 +2583,13 @@
         <v>0.1773</v>
       </c>
       <c r="AG19">
-        <v>0.7696</v>
+        <v>0.773</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2648,7 +2648,7 @@
         <v>0.381</v>
       </c>
       <c r="S20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T20">
         <v>0.2167</v>
@@ -2663,7 +2663,7 @@
         <v>0.2173</v>
       </c>
       <c r="X20">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y20">
         <v>0.9878</v>
@@ -2675,7 +2675,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2684,13 +2684,13 @@
         <v>0.1803</v>
       </c>
       <c r="AG20">
-        <v>0.9935</v>
+        <v>0.998</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2749,25 +2749,25 @@
         <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.1828</v>
+        <v>0.1841</v>
       </c>
       <c r="U21">
-        <v>0.1845</v>
+        <v>0.184</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>0.2161</v>
       </c>
       <c r="X21">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y21">
-        <v>0.9905</v>
+        <v>1.0063</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2776,7 +2776,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.51</v>
+        <v>5.66</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2785,13 +2785,13 @@
         <v>0.3009</v>
       </c>
       <c r="AG21">
-        <v>0.8383</v>
+        <v>0.8479</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.51</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2850,7 +2850,7 @@
         <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T22">
         <v>0.1979</v>
@@ -2865,7 +2865,7 @@
         <v>0.2371</v>
       </c>
       <c r="X22">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y22">
         <v>1.0167</v>
@@ -2877,7 +2877,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2886,13 +2886,13 @@
         <v>0.2099</v>
       </c>
       <c r="AG22">
-        <v>0.9075</v>
+        <v>0.9116</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2951,7 +2951,7 @@
         <v>0.371</v>
       </c>
       <c r="S23" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T23">
         <v>0.2579</v>
@@ -2966,7 +2966,7 @@
         <v>0.2132</v>
       </c>
       <c r="X23">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y23">
         <v>1.0394</v>
@@ -2978,7 +2978,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>7.57</v>
+        <v>7.6</v>
       </c>
       <c r="AE23" t="s">
         <v>64</v>
@@ -2987,13 +2987,13 @@
         <v>0.2571</v>
       </c>
       <c r="AG23">
-        <v>1.1825</v>
+        <v>1.1878</v>
       </c>
       <c r="AH23">
         <v>-0.6</v>
       </c>
       <c r="AM23">
-        <v>6.97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3067,7 +3067,7 @@
         <v>0.2191</v>
       </c>
       <c r="X24">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y24">
         <v>0.9649</v>
@@ -3079,7 +3079,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3088,13 +3088,13 @@
         <v>0.2397</v>
       </c>
       <c r="AG24">
-        <v>0.9151</v>
+        <v>0.9192</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3153,13 +3153,13 @@
         <v>0.371</v>
       </c>
       <c r="S25" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2402</v>
+        <v>0.2449</v>
       </c>
       <c r="U25">
-        <v>0.2195</v>
+        <v>0.2248</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -3168,10 +3168,10 @@
         <v>0.2254</v>
       </c>
       <c r="X25">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y25">
-        <v>1.0109</v>
+        <v>0.9915</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3180,7 +3180,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.65</v>
+        <v>6.68</v>
       </c>
       <c r="AE25" t="s">
         <v>49</v>
@@ -3189,13 +3189,13 @@
         <v>0.2618</v>
       </c>
       <c r="AG25">
-        <v>1.1012</v>
+        <v>1.128</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.65</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3254,7 +3254,7 @@
         <v>0.355</v>
       </c>
       <c r="S26" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T26">
         <v>0.1484</v>
@@ -3269,7 +3269,7 @@
         <v>0.2203</v>
       </c>
       <c r="X26">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y26">
         <v>0.9783</v>
@@ -3281,7 +3281,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3290,13 +3290,13 @@
         <v>0.1705</v>
       </c>
       <c r="AG26">
-        <v>0.6805</v>
+        <v>0.6835</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
         <v>0.392</v>
       </c>
       <c r="S27" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="T27">
         <v>0.2064</v>
@@ -3370,7 +3370,7 @@
         <v>0.2044</v>
       </c>
       <c r="X27">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y27">
         <v>0.9925</v>
@@ -3382,7 +3382,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3391,13 +3391,13 @@
         <v>0.1693</v>
       </c>
       <c r="AG27">
-        <v>0.9465</v>
+        <v>0.9507</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3456,13 +3456,13 @@
         <v>0.303</v>
       </c>
       <c r="S28" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.3635</v>
+        <v>0.2786</v>
       </c>
       <c r="U28">
-        <v>0.2882</v>
+        <v>0.2862</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -3471,10 +3471,10 @@
         <v>0.2558</v>
       </c>
       <c r="X28">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="Y28">
-        <v>1.046</v>
+        <v>1.0996</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3483,22 +3483,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.51</v>
+        <v>5.26</v>
       </c>
       <c r="AE28" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF28">
         <v>0.1809</v>
       </c>
       <c r="AG28">
-        <v>1.6668</v>
+        <v>1.2832</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>6.51</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -151,6 +151,12 @@
     <t>&lt;6</t>
   </si>
   <si>
+    <t>Jackson Jobe</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Payton Tolle</t>
   </si>
   <si>
@@ -187,9 +193,6 @@
     <t>Max Scherzer</t>
   </si>
   <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
     <t>Kyle Harrison</t>
   </si>
   <si>
@@ -205,18 +208,18 @@
     <t>Los Angeles Dodgers @ Atlanta Braves</t>
   </si>
   <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
     <t>Anthony Kay</t>
   </si>
   <si>
@@ -238,9 +241,6 @@
     <t>Walbert Ureña</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
     <t>Clay Holmes</t>
   </si>
   <si>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>Adrian Houser</t>
-  </si>
-  <si>
-    <t>Jackson Jobe</t>
   </si>
   <si>
     <t>Ian Seymour</t>
@@ -818,7 +815,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -830,22 +827,22 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0.1799</v>
+        <v>0.1822</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="Q2">
-        <v>0.129</v>
+        <v>0.1563</v>
       </c>
       <c r="R2">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -863,7 +860,7 @@
         <v>0.2237</v>
       </c>
       <c r="X2">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y2">
         <v>0.906</v>
@@ -875,22 +872,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1731</v>
+        <v>0.1786</v>
       </c>
       <c r="AG2">
-        <v>0.8967</v>
+        <v>0.8909</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -901,25 +898,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E3">
-        <v>-137</v>
+        <v>-132</v>
       </c>
       <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>824233</v>
+      </c>
+      <c r="H3" t="s">
         <v>47</v>
       </c>
-      <c r="G3">
-        <v>823826</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
-      </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -928,46 +925,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>0.2774</v>
+        <v>0.1818</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="Q3">
-        <v>0.3276</v>
+        <v>0.1867</v>
       </c>
       <c r="R3">
-        <v>0.367</v>
+        <v>0.273</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2391</v>
+        <v>0.1597</v>
       </c>
       <c r="U3">
-        <v>0.2122</v>
+        <v>0.1589</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2307</v>
+        <v>0.1874</v>
       </c>
       <c r="X3">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y3">
-        <v>0.8824</v>
+        <v>0.88</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -976,22 +973,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>6.61</v>
+        <v>2.27</v>
       </c>
       <c r="AE3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2958</v>
+        <v>0.1831</v>
       </c>
       <c r="AG3">
-        <v>1.1015</v>
+        <v>0.731</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>6.61</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -999,28 +996,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D4">
-        <v>-120</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>116</v>
+        <v>-137</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>823826</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1032,43 +1029,43 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.182</v>
+        <v>0.2823</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="P4">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>0.2</v>
+        <v>0.3462</v>
       </c>
       <c r="R4">
-        <v>0.333</v>
+        <v>0.342</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1854</v>
+        <v>0.2391</v>
       </c>
       <c r="U4">
-        <v>0.199</v>
+        <v>0.2122</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2139</v>
+        <v>0.2307</v>
       </c>
       <c r="X4">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y4">
-        <v>0.9777</v>
+        <v>0.8824</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1077,22 +1074,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.09</v>
+        <v>6.62</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF4">
-        <v>0.188</v>
+        <v>0.3041</v>
       </c>
       <c r="AG4">
-        <v>0.854</v>
+        <v>1.0944</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.09</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1100,29 +1097,29 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
+        <v>3.5</v>
+      </c>
+      <c r="D5">
+        <v>-120</v>
+      </c>
+      <c r="E5">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5">
+        <v>823826</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5">
         <v>4.5</v>
       </c>
-      <c r="D5">
-        <v>-130</v>
-      </c>
-      <c r="E5">
-        <v>109</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>822693</v>
-      </c>
-      <c r="H5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5">
-        <v>4.8</v>
-      </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
@@ -1130,46 +1127,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2183</v>
+        <v>0.1885</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="P5">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="Q5">
-        <v>0.1667</v>
+        <v>0.2424</v>
       </c>
       <c r="R5">
-        <v>0.351</v>
+        <v>0.331</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2643</v>
+        <v>0.1854</v>
       </c>
       <c r="U5">
-        <v>0.2432</v>
+        <v>0.199</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2478</v>
+        <v>0.2139</v>
       </c>
       <c r="X5">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y5">
-        <v>1.0972</v>
+        <v>0.9777</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1178,22 +1175,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.49</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2002</v>
+        <v>0.2063</v>
       </c>
       <c r="AG5">
-        <v>1.2174</v>
+        <v>0.8484</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.49</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1207,22 +1204,22 @@
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-135</v>
+        <v>-130</v>
       </c>
       <c r="E6">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
       </c>
       <c r="G6">
-        <v>823505</v>
+        <v>822693</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1231,46 +1228,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>0.228</v>
+        <v>0.2222</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P6">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="Q6">
-        <v>0.2451</v>
+        <v>0.202</v>
       </c>
       <c r="R6">
-        <v>0.338</v>
+        <v>0.331</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2167</v>
+        <v>0.2643</v>
       </c>
       <c r="U6">
-        <v>0.2115</v>
+        <v>0.2432</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2189</v>
+        <v>0.2478</v>
       </c>
       <c r="X6">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y6">
-        <v>0.9612</v>
+        <v>1.0972</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1279,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.97</v>
+        <v>5.68</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2338</v>
+        <v>0.2155</v>
       </c>
       <c r="AG6">
-        <v>0.9982</v>
+        <v>1.2096</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.97</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1305,25 +1302,25 @@
         <v>55</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-130</v>
+        <v>-135</v>
       </c>
       <c r="E7">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
       </c>
       <c r="G7">
-        <v>822773</v>
+        <v>823505</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1335,43 +1332,43 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.1793</v>
+        <v>0.2275</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="P7">
-        <v>4.26</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>0.1417</v>
+        <v>0.2316</v>
       </c>
       <c r="R7">
-        <v>0.375</v>
+        <v>0.322</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2005</v>
+        <v>0.2167</v>
       </c>
       <c r="U7">
-        <v>0.1876</v>
+        <v>0.2115</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.189</v>
+        <v>0.2189</v>
       </c>
       <c r="X7">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y7">
-        <v>0.9732</v>
+        <v>0.9612</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1380,22 +1377,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.53</v>
+        <v>4.73</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1652</v>
+        <v>0.2288</v>
       </c>
       <c r="AG7">
-        <v>0.9235</v>
+        <v>0.9917</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.53</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1409,22 +1406,22 @@
         <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-140</v>
+        <v>-130</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>822773</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,43 +1433,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1584</v>
+        <v>0.1792</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P8">
-        <v>4.49</v>
+        <v>4.27</v>
       </c>
       <c r="Q8">
-        <v>0.18</v>
+        <v>0.1569</v>
       </c>
       <c r="R8">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1732</v>
+        <v>0.2005</v>
       </c>
       <c r="U8">
-        <v>0.1849</v>
+        <v>0.1876</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.208</v>
+        <v>0.189</v>
       </c>
       <c r="X8">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y8">
-        <v>0.8979</v>
+        <v>0.9732</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1481,22 +1478,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1656</v>
+        <v>0.1717</v>
       </c>
       <c r="AG8">
-        <v>0.7978</v>
+        <v>0.9175</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,25 +1504,25 @@
         <v>59</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9">
-        <v>-114</v>
+        <v>-140</v>
       </c>
       <c r="E9">
         <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>823585</v>
+        <v>822773</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1537,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.3035</v>
+        <v>0.1571</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -1546,10 +1543,10 @@
         <v>93</v>
       </c>
       <c r="P9">
-        <v>4.09</v>
+        <v>4.53</v>
       </c>
       <c r="Q9">
-        <v>0.2796</v>
+        <v>0.1613</v>
       </c>
       <c r="R9">
         <v>0.317</v>
@@ -1558,22 +1555,22 @@
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.1933</v>
+        <v>0.1732</v>
       </c>
       <c r="U9">
-        <v>0.2049</v>
+        <v>0.1849</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2322</v>
+        <v>0.208</v>
       </c>
       <c r="X9">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y9">
-        <v>0.9313</v>
+        <v>0.8979</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1582,22 +1579,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.93</v>
+        <v>1.97</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2959</v>
+        <v>0.1585</v>
       </c>
       <c r="AG9">
-        <v>0.8903</v>
+        <v>0.7926</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.93</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1605,19 +1602,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>5.5</v>
+      </c>
+      <c r="D10">
+        <v>-114</v>
+      </c>
+      <c r="E10">
+        <v>120</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
       </c>
       <c r="G10">
         <v>823585</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1626,46 +1632,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.18</v>
+        <v>0.3024</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>3.97</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>0.1681</v>
+        <v>0.2824</v>
       </c>
       <c r="R10">
-        <v>0.361</v>
+        <v>0.298</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2334</v>
+        <v>0.1933</v>
       </c>
       <c r="U10">
-        <v>0.2268</v>
+        <v>0.2049</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2197</v>
+        <v>0.2322</v>
       </c>
       <c r="X10">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y10">
-        <v>0.9845</v>
+        <v>0.9313</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1674,22 +1680,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.13</v>
+        <v>4.77</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1757</v>
+        <v>0.2964</v>
       </c>
       <c r="AG10">
-        <v>1.075</v>
+        <v>0.8845</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.13</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1699,26 +1705,17 @@
       <c r="B11" t="s">
         <v>62</v>
       </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>-160</v>
-      </c>
-      <c r="E11">
-        <v>130</v>
-      </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>824881</v>
+        <v>823585</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1727,31 +1724,31 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0.3311</v>
+        <v>0.1796</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P11">
-        <v>3.73</v>
+        <v>3.94</v>
       </c>
       <c r="Q11">
-        <v>0.3366</v>
+        <v>0.1563</v>
       </c>
       <c r="R11">
-        <v>0.336</v>
+        <v>0.324</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2367</v>
+        <v>0.2334</v>
       </c>
       <c r="U11">
         <v>0.2268</v>
@@ -1760,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2195</v>
+        <v>0.2197</v>
       </c>
       <c r="X11">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y11">
-        <v>0.9769</v>
+        <v>0.9845</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1775,22 +1772,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.5</v>
+        <v>3.73</v>
       </c>
       <c r="AE11" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.3329</v>
+        <v>0.172</v>
       </c>
       <c r="AG11">
-        <v>1.09</v>
+        <v>1.068</v>
       </c>
       <c r="AH11">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>6.9</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1798,28 +1795,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>128</v>
+        <v>-160</v>
       </c>
       <c r="E12">
-        <v>-152</v>
+        <v>130</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>824881</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1831,43 +1828,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1952</v>
+        <v>0.3161</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>3.84</v>
       </c>
       <c r="Q12">
-        <v>0.1885</v>
+        <v>0.3293</v>
       </c>
       <c r="R12">
-        <v>0.379</v>
+        <v>0.291</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2135</v>
+        <v>0.2367</v>
       </c>
       <c r="U12">
-        <v>0.1988</v>
+        <v>0.2268</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2072</v>
+        <v>0.2195</v>
       </c>
       <c r="X12">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y12">
-        <v>0.9474</v>
+        <v>0.9769</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1876,22 +1873,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.33</v>
+        <v>6.56</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF12">
-        <v>0.1926</v>
+        <v>0.3199</v>
       </c>
       <c r="AG12">
-        <v>0.9834</v>
+        <v>1.083</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.33</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1899,28 +1896,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D13">
-        <v>-108</v>
+        <v>128</v>
       </c>
       <c r="E13">
-        <v>-105</v>
+        <v>-152</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>824556</v>
+        <v>824881</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1932,43 +1929,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.3031</v>
+        <v>0.1942</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="P13">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>0.3085</v>
+        <v>0.1456</v>
       </c>
       <c r="R13">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2481</v>
+        <v>0.2135</v>
       </c>
       <c r="U13">
-        <v>0.2564</v>
+        <v>0.1988</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2377</v>
+        <v>0.2072</v>
       </c>
       <c r="X13">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y13">
-        <v>1.0634</v>
+        <v>0.9474</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1977,22 +1974,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.99</v>
+        <v>3.83</v>
       </c>
       <c r="AE13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.3048</v>
+        <v>0.1777</v>
       </c>
       <c r="AG13">
-        <v>1.1427</v>
+        <v>0.977</v>
       </c>
       <c r="AH13">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>7.39</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2000,16 +1997,16 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D14">
-        <v>-120</v>
+        <v>-108</v>
       </c>
       <c r="E14">
-        <v>105</v>
+        <v>-105</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
@@ -2018,10 +2015,10 @@
         <v>824556</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2033,43 +2030,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1841</v>
+        <v>0.3031</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="P14">
-        <v>4.44</v>
+        <v>4.09</v>
       </c>
       <c r="Q14">
-        <v>0.1983</v>
+        <v>0.3085</v>
       </c>
       <c r="R14">
-        <v>0.377</v>
+        <v>0.32</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2569</v>
+        <v>0.2481</v>
       </c>
       <c r="U14">
-        <v>0.234</v>
+        <v>0.2564</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2428</v>
+        <v>0.2377</v>
       </c>
       <c r="X14">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y14">
-        <v>1.046</v>
+        <v>1.0634</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2078,22 +2075,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.22</v>
+        <v>7.94</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AF14">
-        <v>0.1895</v>
+        <v>0.3048</v>
       </c>
       <c r="AG14">
-        <v>1.1834</v>
+        <v>1.1353</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM14">
-        <v>5.22</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2104,25 +2101,25 @@
         <v>69</v>
       </c>
       <c r="C15">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D15">
         <v>-120</v>
       </c>
       <c r="E15">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>823016</v>
+        <v>824556</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2134,43 +2131,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1489</v>
+        <v>0.1841</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="P15">
-        <v>4.59</v>
+        <v>4.44</v>
       </c>
       <c r="Q15">
-        <v>0.1455</v>
+        <v>0.1983</v>
       </c>
       <c r="R15">
-        <v>0.355</v>
+        <v>0.377</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.1757</v>
+        <v>0.2569</v>
       </c>
       <c r="U15">
-        <v>0.1924</v>
+        <v>0.234</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2142</v>
+        <v>0.2428</v>
       </c>
       <c r="X15">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y15">
-        <v>0.9745</v>
+        <v>1.046</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2179,22 +2176,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.54</v>
+        <v>5.18</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1477</v>
+        <v>0.1895</v>
       </c>
       <c r="AG15">
-        <v>0.8093</v>
+        <v>1.1758</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>2.54</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2202,19 +2199,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16">
+        <v>3.5</v>
+      </c>
+      <c r="D16">
+        <v>-120</v>
+      </c>
+      <c r="E16">
+        <v>104</v>
+      </c>
+      <c r="F16" t="s">
         <v>71</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
       </c>
       <c r="G16">
         <v>823016</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2223,46 +2229,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2311</v>
+        <v>0.1489</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="P16">
-        <v>4.33</v>
+        <v>4.59</v>
       </c>
       <c r="Q16">
-        <v>0.2885</v>
+        <v>0.1455</v>
       </c>
       <c r="R16">
-        <v>0.342</v>
+        <v>0.355</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2457</v>
+        <v>0.1757</v>
       </c>
       <c r="U16">
-        <v>0.235</v>
+        <v>0.1924</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>0.2573</v>
+        <v>0.2142</v>
       </c>
       <c r="X16">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y16">
-        <v>1.0581</v>
+        <v>0.9745</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2271,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.5</v>
+        <v>2.52</v>
       </c>
       <c r="AE16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2507</v>
+        <v>0.1477</v>
       </c>
       <c r="AG16">
-        <v>1.1316</v>
+        <v>0.8041</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.5</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2296,26 +2302,17 @@
       <c r="B17" t="s">
         <v>72</v>
       </c>
-      <c r="C17">
-        <v>8.5</v>
-      </c>
-      <c r="D17">
-        <v>116</v>
-      </c>
-      <c r="E17">
-        <v>-138</v>
-      </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G17">
-        <v>823989</v>
+        <v>823016</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I17">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2324,46 +2321,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0.3237</v>
+        <v>0.2311</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="P17">
-        <v>4.02</v>
+        <v>4.33</v>
       </c>
       <c r="Q17">
-        <v>0.3982</v>
+        <v>0.2885</v>
       </c>
       <c r="R17">
-        <v>0.361</v>
+        <v>0.342</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.278</v>
+        <v>0.2457</v>
       </c>
       <c r="U17">
-        <v>0.2646</v>
+        <v>0.235</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2511</v>
+        <v>0.2573</v>
       </c>
       <c r="X17">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y17">
-        <v>1.0831</v>
+        <v>1.0581</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2372,22 +2369,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>11.61</v>
+        <v>6.45</v>
       </c>
       <c r="AE17" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="AF17">
-        <v>0.3506</v>
+        <v>0.2507</v>
       </c>
       <c r="AG17">
-        <v>1.2804</v>
+        <v>1.1243</v>
       </c>
       <c r="AH17">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>11.01</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2395,28 +2392,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18">
+        <v>8.5</v>
+      </c>
+      <c r="D18">
+        <v>116</v>
+      </c>
+      <c r="E18">
+        <v>-138</v>
+      </c>
+      <c r="F18" t="s">
         <v>74</v>
-      </c>
-      <c r="C18">
-        <v>4.5</v>
-      </c>
-      <c r="D18">
-        <v>130</v>
-      </c>
-      <c r="E18">
-        <v>-155</v>
-      </c>
-      <c r="F18" t="s">
-        <v>73</v>
       </c>
       <c r="G18">
         <v>823989</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2428,43 +2425,43 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>0.2276</v>
+        <v>0.3237</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P18">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="Q18">
-        <v>0.2574</v>
+        <v>0.3982</v>
       </c>
       <c r="R18">
-        <v>0.336</v>
+        <v>0.361</v>
       </c>
       <c r="S18" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2037</v>
+        <v>0.278</v>
       </c>
       <c r="U18">
-        <v>0.1828</v>
+        <v>0.2646</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2107</v>
+        <v>0.2511</v>
       </c>
       <c r="X18">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y18">
-        <v>0.9595</v>
+        <v>1.0831</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2473,22 +2470,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.81</v>
+        <v>11.54</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AF18">
-        <v>0.2376</v>
+        <v>0.3506</v>
       </c>
       <c r="AG18">
-        <v>0.9382</v>
+        <v>1.2721</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AM18">
-        <v>4.81</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2496,28 +2493,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E19">
-        <v>-132</v>
+        <v>-155</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G19">
-        <v>825042</v>
+        <v>823989</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2526,46 +2523,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>0.1799</v>
+        <v>0.2276</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="P19">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="Q19">
-        <v>0.1727</v>
+        <v>0.2574</v>
       </c>
       <c r="R19">
-        <v>0.355</v>
+        <v>0.336</v>
       </c>
       <c r="S19" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1678</v>
+        <v>0.1876</v>
       </c>
       <c r="U19">
-        <v>0.1685</v>
+        <v>0.1845</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.1976</v>
+        <v>0.2107</v>
       </c>
       <c r="X19">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y19">
-        <v>0.9284</v>
+        <v>0.9042</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2574,22 +2571,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.95</v>
+        <v>4.15</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1773</v>
+        <v>0.2376</v>
       </c>
       <c r="AG19">
-        <v>0.773</v>
+        <v>0.8587</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>2.95</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2597,16 +2594,16 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D20">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E20">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="F20" t="s">
         <v>77</v>
@@ -2615,10 +2612,10 @@
         <v>825042</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I20">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2630,43 +2627,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.1712</v>
+        <v>0.1799</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="P20">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q20">
-        <v>0.1951</v>
+        <v>0.1727</v>
       </c>
       <c r="R20">
-        <v>0.381</v>
+        <v>0.355</v>
       </c>
       <c r="S20" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2167</v>
+        <v>0.1937</v>
       </c>
       <c r="U20">
-        <v>0.2155</v>
+        <v>0.1757</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2173</v>
+        <v>0.1976</v>
       </c>
       <c r="X20">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y20">
-        <v>0.9878</v>
+        <v>0.88</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2675,22 +2672,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.32</v>
+        <v>3.2</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.1803</v>
+        <v>0.1773</v>
       </c>
       <c r="AG20">
-        <v>0.998</v>
+        <v>0.8864</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.32</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2698,28 +2695,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-154</v>
+        <v>116</v>
       </c>
       <c r="E21">
-        <v>128</v>
+        <v>-135</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G21">
-        <v>823259</v>
+        <v>825042</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2731,43 +2728,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2984</v>
+        <v>0.1712</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="P21">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="Q21">
-        <v>0.3056</v>
+        <v>0.1951</v>
       </c>
       <c r="R21">
-        <v>0.351</v>
+        <v>0.381</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.1841</v>
+        <v>0.2308</v>
       </c>
       <c r="U21">
-        <v>0.184</v>
+        <v>0.2219</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2161</v>
+        <v>0.2173</v>
       </c>
       <c r="X21">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y21">
-        <v>1.0063</v>
+        <v>0.9663</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2776,22 +2773,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.66</v>
+        <v>4.47</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.3009</v>
+        <v>0.1803</v>
       </c>
       <c r="AG21">
-        <v>0.8479</v>
+        <v>1.0563</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.66</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2799,16 +2796,16 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>5.5</v>
       </c>
       <c r="D22">
-        <v>-105</v>
+        <v>-154</v>
       </c>
       <c r="E22">
-        <v>-111</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -2817,10 +2814,10 @@
         <v>823259</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2832,43 +2829,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2098</v>
+        <v>0.2984</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="P22">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="Q22">
-        <v>0.2101</v>
+        <v>0.3056</v>
       </c>
       <c r="R22">
-        <v>0.373</v>
+        <v>0.351</v>
       </c>
       <c r="S22" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.1979</v>
+        <v>0.1841</v>
       </c>
       <c r="U22">
-        <v>0.2227</v>
+        <v>0.184</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2371</v>
+        <v>0.2161</v>
       </c>
       <c r="X22">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y22">
-        <v>1.0167</v>
+        <v>1.0063</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2877,22 +2874,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.56</v>
+        <v>5.62</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2099</v>
+        <v>0.3009</v>
       </c>
       <c r="AG22">
-        <v>0.9116</v>
+        <v>0.8424</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.56</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2900,7 +2897,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2909,19 +2906,19 @@
         <v>-105</v>
       </c>
       <c r="E23">
-        <v>-104</v>
+        <v>-111</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G23">
-        <v>824962</v>
+        <v>823259</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2933,40 +2930,40 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2638</v>
+        <v>0.2098</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P23">
-        <v>4.26</v>
+        <v>4.09</v>
       </c>
       <c r="Q23">
-        <v>0.2458</v>
+        <v>0.2101</v>
       </c>
       <c r="R23">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="S23" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2579</v>
+        <v>0.2362</v>
       </c>
       <c r="U23">
-        <v>0.2281</v>
+        <v>0.2286</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2132</v>
+        <v>0.2371</v>
       </c>
       <c r="X23">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y23">
         <v>1.0394</v>
@@ -2978,22 +2975,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>7.6</v>
+        <v>5.53</v>
       </c>
       <c r="AE23" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2571</v>
+        <v>0.2099</v>
       </c>
       <c r="AG23">
-        <v>1.1878</v>
+        <v>1.0807</v>
       </c>
       <c r="AH23">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>7</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3001,16 +2998,16 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D24">
-        <v>-140</v>
+        <v>-105</v>
       </c>
       <c r="E24">
-        <v>130</v>
+        <v>-104</v>
       </c>
       <c r="F24" t="s">
         <v>83</v>
@@ -3019,10 +3016,10 @@
         <v>824962</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I24">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3034,43 +3031,43 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2438</v>
+        <v>0.2638</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="Q24">
-        <v>0.2328</v>
+        <v>0.2458</v>
       </c>
       <c r="R24">
-        <v>0.367</v>
+        <v>0.371</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.1996</v>
+        <v>0.198</v>
       </c>
       <c r="U24">
-        <v>0.1929</v>
+        <v>0.1983</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2191</v>
+        <v>0.2132</v>
       </c>
       <c r="X24">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y24">
-        <v>0.9649</v>
+        <v>0.9886</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3079,22 +3076,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.8</v>
+        <v>5.52</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2397</v>
+        <v>0.2571</v>
       </c>
       <c r="AG24">
-        <v>0.9192</v>
+        <v>0.9059</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.8</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3102,28 +3099,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="E25">
-        <v>-104</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G25">
-        <v>823098</v>
+        <v>824962</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I25">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3135,43 +3132,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2462</v>
+        <v>0.2438</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>0.2881</v>
+        <v>0.2328</v>
       </c>
       <c r="R25">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2449</v>
+        <v>0.1996</v>
       </c>
       <c r="U25">
-        <v>0.2248</v>
+        <v>0.1929</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2254</v>
+        <v>0.2191</v>
       </c>
       <c r="X25">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y25">
-        <v>0.9915</v>
+        <v>0.9649</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3180,22 +3177,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.68</v>
+        <v>4.77</v>
       </c>
       <c r="AE25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.2618</v>
+        <v>0.2397</v>
       </c>
       <c r="AG25">
-        <v>1.128</v>
+        <v>0.9132</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.68</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3203,16 +3200,16 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>-114</v>
+        <v>-120</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="F26" t="s">
         <v>86</v>
@@ -3221,10 +3218,10 @@
         <v>823098</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I26">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3236,43 +3233,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1993</v>
+        <v>0.2462</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="P26">
-        <v>4.19</v>
+        <v>4.33</v>
       </c>
       <c r="Q26">
-        <v>0.1182</v>
+        <v>0.2881</v>
       </c>
       <c r="R26">
-        <v>0.355</v>
+        <v>0.371</v>
       </c>
       <c r="S26" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.1484</v>
+        <v>0.2449</v>
       </c>
       <c r="U26">
-        <v>0.1505</v>
+        <v>0.2248</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2203</v>
+        <v>0.2254</v>
       </c>
       <c r="X26">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y26">
-        <v>0.9783</v>
+        <v>0.9915</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3281,22 +3278,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.79</v>
+        <v>6.63</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF26">
-        <v>0.1705</v>
+        <v>0.2618</v>
       </c>
       <c r="AG26">
-        <v>0.6835</v>
+        <v>1.1207</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.79</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3304,28 +3301,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>116</v>
+        <v>-114</v>
       </c>
       <c r="E27">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G27">
-        <v>823181</v>
+        <v>823098</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I27">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3337,43 +3334,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1835</v>
+        <v>0.1993</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="P27">
-        <v>4.43</v>
+        <v>4.19</v>
       </c>
       <c r="Q27">
-        <v>0.1473</v>
+        <v>0.1182</v>
       </c>
       <c r="R27">
-        <v>0.392</v>
+        <v>0.355</v>
       </c>
       <c r="S27" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2064</v>
+        <v>0.1516</v>
       </c>
       <c r="U27">
-        <v>0.2055</v>
+        <v>0.1464</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2044</v>
+        <v>0.2203</v>
       </c>
       <c r="X27">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y27">
-        <v>0.9925</v>
+        <v>0.9566</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3382,22 +3379,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.73</v>
+        <v>2.77</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1693</v>
+        <v>0.1705</v>
       </c>
       <c r="AG27">
-        <v>0.9507</v>
+        <v>0.6937</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.73</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3405,16 +3402,16 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D28">
-        <v>-140</v>
+        <v>116</v>
       </c>
       <c r="E28">
-        <v>123</v>
+        <v>-133</v>
       </c>
       <c r="F28" t="s">
         <v>89</v>
@@ -3423,10 +3420,10 @@
         <v>823181</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I28">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3438,43 +3435,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.1573</v>
+        <v>0.1835</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="P28">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="Q28">
-        <v>0.2529</v>
+        <v>0.1473</v>
       </c>
       <c r="R28">
-        <v>0.303</v>
+        <v>0.392</v>
       </c>
       <c r="S28" t="s">
         <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2786</v>
+        <v>0.2434</v>
       </c>
       <c r="U28">
-        <v>0.2862</v>
+        <v>0.2146</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2558</v>
+        <v>0.2044</v>
       </c>
       <c r="X28">
-        <v>0.2171</v>
+        <v>0.2185</v>
       </c>
       <c r="Y28">
-        <v>1.0996</v>
+        <v>0.9304</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3483,22 +3480,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.26</v>
+        <v>4.09</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.1809</v>
+        <v>0.1693</v>
       </c>
       <c r="AG28">
-        <v>1.2832</v>
+        <v>1.1136</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.26</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3506,34 +3503,76 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>3.5</v>
       </c>
       <c r="D29">
-        <v>107</v>
+        <v>-140</v>
       </c>
       <c r="E29">
-        <v>-132</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="G29">
+        <v>823181</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="I29">
+        <v>4.8</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
       </c>
       <c r="L29">
+        <v>6</v>
+      </c>
+      <c r="M29">
+        <v>0.1573</v>
+      </c>
+      <c r="N29">
         <v>5</v>
       </c>
+      <c r="O29">
+        <v>87</v>
+      </c>
+      <c r="P29">
+        <v>4.3</v>
+      </c>
+      <c r="Q29">
+        <v>0.2529</v>
+      </c>
+      <c r="R29">
+        <v>0.303</v>
+      </c>
       <c r="S29" t="s">
-        <v>44</v>
-      </c>
-      <c r="V29" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T29">
+        <v>0.2786</v>
+      </c>
+      <c r="U29">
+        <v>0.2862</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.2558</v>
+      </c>
+      <c r="X29">
+        <v>0.2185</v>
+      </c>
+      <c r="Y29">
+        <v>1.0996</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3541,8 +3580,23 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
+      <c r="AD29">
+        <v>5.23</v>
+      </c>
       <c r="AE29" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF29">
+        <v>0.1809</v>
+      </c>
+      <c r="AG29">
+        <v>1.2749</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>5.23</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3550,7 +3604,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30">
         <v>5.5</v>
@@ -3568,7 +3622,7 @@
         <v>824233</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I30">
         <v>4.7</v>
@@ -3651,7 +3705,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3663,7 +3717,7 @@
         <v>-143</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -3695,7 +3749,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3707,7 +3761,7 @@
         <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-25.xlsx
+++ b/data/k-props/2026-08-25.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -157,6 +157,12 @@
     <t>Limited starter</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>Payton Tolle</t>
   </si>
   <si>
@@ -178,10 +184,16 @@
     <t>Colorado Rockies @ Washington Nationals</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>Will Warren</t>
   </si>
   <si>
     <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
   <si>
     <t>Seth Lugo</t>
@@ -966,11 +978,17 @@
       <c r="Y3">
         <v>0.88</v>
       </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>-1.23</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD3">
         <v>2.27</v>
@@ -986,6 +1004,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>1.73</v>
+      </c>
+      <c r="AJ3">
+        <v>1.73</v>
+      </c>
+      <c r="AK3">
+        <v>1.73</v>
+      </c>
+      <c r="AL3">
+        <v>1.73</v>
       </c>
       <c r="AM3">
         <v>2.27</v>
@@ -996,7 +1026,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>6.5</v>
@@ -1008,13 +1038,13 @@
         <v>-137</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>823826</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I4">
         <v>5.6</v>
@@ -1067,8 +1097,14 @@
       <c r="Y4">
         <v>0.8824</v>
       </c>
+      <c r="Z4">
+        <v>7</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB4">
+        <v>0.12</v>
       </c>
       <c r="AC4" t="s">
         <v>44</v>
@@ -1077,7 +1113,7 @@
         <v>6.62</v>
       </c>
       <c r="AE4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF4">
         <v>0.3041</v>
@@ -1087,6 +1123,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0.38</v>
+      </c>
+      <c r="AJ4">
+        <v>0.38</v>
+      </c>
+      <c r="AK4">
+        <v>0.38</v>
+      </c>
+      <c r="AL4">
+        <v>0.38</v>
       </c>
       <c r="AM4">
         <v>6.62</v>
@@ -1097,7 +1145,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>3.5</v>
@@ -1109,13 +1157,13 @@
         <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>823826</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I5">
         <v>4.5</v>
@@ -1168,8 +1216,14 @@
       <c r="Y5">
         <v>0.9777</v>
       </c>
+      <c r="Z5">
+        <v>7</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB5">
+        <v>-0.16</v>
       </c>
       <c r="AC5" t="s">
         <v>44</v>
@@ -1188,6 +1242,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>3.66</v>
+      </c>
+      <c r="AJ5">
+        <v>3.66</v>
+      </c>
+      <c r="AK5">
+        <v>3.66</v>
+      </c>
+      <c r="AL5">
+        <v>3.66</v>
       </c>
       <c r="AM5">
         <v>3.34</v>
@@ -1198,7 +1264,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1210,13 +1276,13 @@
         <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>822693</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I6">
         <v>4.7</v>
@@ -1269,11 +1335,17 @@
       <c r="Y6">
         <v>1.0972</v>
       </c>
+      <c r="Z6">
+        <v>6</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB6">
+        <v>1.18</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD6">
         <v>5.68</v>
@@ -1289,6 +1361,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0.32</v>
+      </c>
+      <c r="AJ6">
+        <v>0.32</v>
+      </c>
+      <c r="AK6">
+        <v>0.32</v>
+      </c>
+      <c r="AL6">
+        <v>0.32</v>
       </c>
       <c r="AM6">
         <v>5.68</v>
@@ -1299,7 +1383,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1311,13 +1395,13 @@
         <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>823505</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I7">
         <v>4.9</v>
@@ -1370,8 +1454,14 @@
       <c r="Y7">
         <v>0.9612</v>
       </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB7">
+        <v>0.23</v>
       </c>
       <c r="AC7" t="s">
         <v>44</v>
@@ -1390,6 +1480,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-0.73</v>
+      </c>
+      <c r="AJ7">
+        <v>0.73</v>
+      </c>
+      <c r="AK7">
+        <v>-0.73</v>
+      </c>
+      <c r="AL7">
+        <v>0.73</v>
       </c>
       <c r="AM7">
         <v>4.73</v>
@@ -1400,7 +1502,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1412,13 +1514,13 @@
         <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>822773</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I8">
         <v>5.4</v>
@@ -1471,8 +1573,14 @@
       <c r="Y8">
         <v>0.9732</v>
       </c>
+      <c r="Z8">
+        <v>5</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB8">
+        <v>0.05</v>
       </c>
       <c r="AC8" t="s">
         <v>44</v>
@@ -1491,6 +1599,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>1.45</v>
+      </c>
+      <c r="AJ8">
+        <v>1.45</v>
+      </c>
+      <c r="AK8">
+        <v>1.45</v>
+      </c>
+      <c r="AL8">
+        <v>1.45</v>
       </c>
       <c r="AM8">
         <v>3.55</v>
@@ -1501,7 +1621,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1513,7 +1633,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>822773</v>
@@ -1572,11 +1692,17 @@
       <c r="Y9">
         <v>0.8979</v>
       </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB9">
+        <v>-1.53</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD9">
         <v>1.97</v>
@@ -1592,6 +1718,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>2.03</v>
+      </c>
+      <c r="AJ9">
+        <v>2.03</v>
+      </c>
+      <c r="AK9">
+        <v>2.03</v>
+      </c>
+      <c r="AL9">
+        <v>2.03</v>
       </c>
       <c r="AM9">
         <v>1.97</v>
@@ -1602,7 +1740,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>5.5</v>
@@ -1614,13 +1752,13 @@
         <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>823585</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I10">
         <v>4.8</v>
@@ -1673,11 +1811,17 @@
       <c r="Y10">
         <v>0.9313</v>
       </c>
+      <c r="Z10">
+        <v>5</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB10">
+        <v>-0.73</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD10">
         <v>4.77</v>
@@ -1693,6 +1837,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0.23</v>
+      </c>
+      <c r="AJ10">
+        <v>0.23</v>
+      </c>
+      <c r="AK10">
+        <v>0.23</v>
+      </c>
+      <c r="AL10">
+        <v>0.23</v>
       </c>
       <c r="AM10">
         <v>4.77</v>
@@ -1703,16 +1859,16 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>823585</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I11">
         <v>5.2</v>
@@ -1795,7 +1951,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1807,13 +1963,13 @@
         <v>130</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>824881</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I12">
         <v>5</v>
@@ -1866,17 +2022,23 @@
       <c r="Y12">
         <v>0.9769</v>
       </c>
+      <c r="Z12">
+        <v>7</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>1.06</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD12">
         <v>6.56</v>
       </c>
       <c r="AE12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF12">
         <v>0.3199</v>
@@ -1886,6 +2048,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0.44</v>
+      </c>
+      <c r="AJ12">
+        <v>0.44</v>
+      </c>
+      <c r="AK12">
+        <v>0.44</v>
+      </c>
+      <c r="AL12">
+        <v>0.44</v>
       </c>
       <c r="AM12">
         <v>6.56</v>
@@ -1896,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1908,13 +2082,13 @@
         <v>-152</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>824881</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I13">
         <v>5.5</v>
@@ -1967,8 +2141,14 @@
       <c r="Y13">
         <v>0.9474</v>
       </c>
+      <c r="Z13">
+        <v>5</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB13">
+        <v>-0.67</v>
       </c>
       <c r="AC13" t="s">
         <v>44</v>
@@ -1987,6 +2167,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>1.17</v>
+      </c>
+      <c r="AJ13">
+        <v>1.17</v>
+      </c>
+      <c r="AK13">
+        <v>1.17</v>
+      </c>
+      <c r="AL13">
+        <v>1.17</v>
       </c>
       <c r="AM13">
         <v>3.83</v>
@@ -1997,7 +2189,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>6.5</v>
@@ -2009,13 +2201,13 @@
         <v>-105</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>824556</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I14">
         <v>5.3</v>
@@ -2068,17 +2260,23 @@
       <c r="Y14">
         <v>1.0634</v>
       </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB14">
+        <v>0.84</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD14">
         <v>7.94</v>
       </c>
       <c r="AE14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AF14">
         <v>0.3048</v>
@@ -2088,6 +2286,18 @@
       </c>
       <c r="AH14">
         <v>-0.6</v>
+      </c>
+      <c r="AI14">
+        <v>-5.94</v>
+      </c>
+      <c r="AJ14">
+        <v>5.94</v>
+      </c>
+      <c r="AK14">
+        <v>-5.34</v>
+      </c>
+      <c r="AL14">
+        <v>5.34</v>
       </c>
       <c r="AM14">
         <v>7.34</v>
@@ -2098,7 +2308,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2110,13 +2320,13 @@
         <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15">
         <v>824556</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -2169,8 +2379,14 @@
       <c r="Y15">
         <v>1.046</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB15">
+        <v>0.68</v>
       </c>
       <c r="AC15" t="s">
         <v>44</v>
@@ -2189,6 +2405,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-1.18</v>
+      </c>
+      <c r="AJ15">
+        <v>1.18</v>
+      </c>
+      <c r="AK15">
+        <v>-1.18</v>
+      </c>
+      <c r="AL15">
+        <v>1.18</v>
       </c>
       <c r="AM15">
         <v>5.18</v>
@@ -2199,7 +2427,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2211,13 +2439,13 @@
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G16">
         <v>823016</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I16">
         <v>4.8</v>
@@ -2270,11 +2498,17 @@
       <c r="Y16">
         <v>0.9745</v>
       </c>
+      <c r="Z16">
+        <v>5</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB16">
+        <v>-0.98</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD16">
         <v>2.52</v>
@@ -2290,6 +2524,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>2.48</v>
+      </c>
+      <c r="AJ16">
+        <v>2.48</v>
+      </c>
+      <c r="AK16">
+        <v>2.48</v>
+      </c>
+      <c r="AL16">
+        <v>2.48</v>
       </c>
       <c r="AM16">
         <v>2.52</v>
@@ -2300,16 +2546,16 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17">
         <v>823016</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -2372,7 +2618,7 @@
         <v>6.45</v>
       </c>
       <c r="AE17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF17">
         <v>0.2507</v>
@@ -2392,7 +2638,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C18">
         <v>8.5</v>
@@ -2404,13 +2650,13 @@
         <v>-138</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G18">
         <v>823989</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I18">
         <v>5.9</v>
@@ -2463,17 +2709,23 @@
       <c r="Y18">
         <v>1.0831</v>
       </c>
+      <c r="Z18">
+        <v>3</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB18">
+        <v>2.44</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD18">
         <v>11.54</v>
       </c>
       <c r="AE18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AF18">
         <v>0.3506</v>
@@ -2483,6 +2735,18 @@
       </c>
       <c r="AH18">
         <v>-0.6</v>
+      </c>
+      <c r="AI18">
+        <v>-8.54</v>
+      </c>
+      <c r="AJ18">
+        <v>8.54</v>
+      </c>
+      <c r="AK18">
+        <v>-7.94</v>
+      </c>
+      <c r="AL18">
+        <v>7.94</v>
       </c>
       <c r="AM18">
         <v>10.94</v>
@@ -2493,7 +2757,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2505,13 +2769,13 @@
         <v>-155</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19">
         <v>823989</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I19">
         <v>5.3</v>
@@ -2564,8 +2828,14 @@
       <c r="Y19">
         <v>0.9042</v>
       </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB19">
+        <v>-0.35</v>
       </c>
       <c r="AC19" t="s">
         <v>44</v>
@@ -2584,6 +2854,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>-1.15</v>
+      </c>
+      <c r="AJ19">
+        <v>1.15</v>
+      </c>
+      <c r="AK19">
+        <v>-1.15</v>
+      </c>
+      <c r="AL19">
+        <v>1.15</v>
       </c>
       <c r="AM19">
         <v>4.15</v>
@@ -2594,7 +2876,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>3.5</v>
@@ -2606,13 +2888,13 @@
         <v>-132</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G20">
         <v>825042</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I20">
         <v>5.7</v>
@@ -2665,8 +2947,14 @@
       <c r="Y20">
         <v>0.88</v>
       </c>
+      <c r="Z20">
+        <v>4</v>
+      </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB20">
+        <v>-0.3</v>
       </c>
       <c r="AC20" t="s">
         <v>44</v>
@@ -2685,6 +2973,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0.8</v>
+      </c>
+      <c r="AJ20">
+        <v>0.8</v>
+      </c>
+      <c r="AK20">
+        <v>0.8</v>
+      </c>
+      <c r="AL20">
+        <v>0.8</v>
       </c>
       <c r="AM20">
         <v>3.2</v>
@@ -2695,7 +2995,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2707,13 +3007,13 @@
         <v>-135</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G21">
         <v>825042</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I21">
         <v>5.9</v>
@@ -2766,8 +3066,14 @@
       <c r="Y21">
         <v>0.9663</v>
       </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB21">
+        <v>-0.03</v>
       </c>
       <c r="AC21" t="s">
         <v>44</v>
@@ -2786,6 +3092,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-1.47</v>
+      </c>
+      <c r="AJ21">
+        <v>1.47</v>
+      </c>
+      <c r="AK21">
+        <v>-1.47</v>
+      </c>
+      <c r="AL21">
+        <v>1.47</v>
       </c>
       <c r="AM21">
         <v>4.47</v>
@@ -2796,7 +3114,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2808,13 +3126,13 @@
         <v>128</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G22">
         <v>823259</v>
       </c>
       <c r="H22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I22">
         <v>5.3</v>
@@ -2867,8 +3185,14 @@
       <c r="Y22">
         <v>1.0063</v>
       </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB22">
+        <v>0.12</v>
       </c>
       <c r="AC22" t="s">
         <v>44</v>
@@ -2887,6 +3211,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-1.62</v>
+      </c>
+      <c r="AJ22">
+        <v>1.62</v>
+      </c>
+      <c r="AK22">
+        <v>-1.62</v>
+      </c>
+      <c r="AL22">
+        <v>1.62</v>
       </c>
       <c r="AM22">
         <v>5.62</v>
@@ -2897,7 +3233,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2909,13 +3245,13 @@
         <v>-111</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>823259</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I23">
         <v>5.7</v>
@@ -2968,8 +3304,14 @@
       <c r="Y23">
         <v>1.0394</v>
       </c>
+      <c r="Z23">
+        <v>7</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB23">
+        <v>0.03</v>
       </c>
       <c r="AC23" t="s">
         <v>44</v>
@@ -2988,6 +3330,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>1.47</v>
+      </c>
+      <c r="AJ23">
+        <v>1.47</v>
+      </c>
+      <c r="AK23">
+        <v>1.47</v>
+      </c>
+      <c r="AL23">
+        <v>1.47</v>
       </c>
       <c r="AM23">
         <v>5.53</v>
@@ -2998,7 +3352,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>5.5</v>
@@ -3010,13 +3364,13 @@
         <v>-104</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24">
         <v>824962</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I24">
         <v>5.6</v>
@@ -3069,8 +3423,14 @@
       <c r="Y24">
         <v>0.9886</v>
       </c>
+      <c r="Z24">
+        <v>9</v>
+      </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB24">
+        <v>0.02</v>
       </c>
       <c r="AC24" t="s">
         <v>44</v>
@@ -3089,6 +3449,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>3.48</v>
+      </c>
+      <c r="AJ24">
+        <v>3.48</v>
+      </c>
+      <c r="AK24">
+        <v>3.48</v>
+      </c>
+      <c r="AL24">
+        <v>3.48</v>
       </c>
       <c r="AM24">
         <v>5.52</v>
@@ -3099,7 +3471,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>4.5</v>
@@ -3111,13 +3483,13 @@
         <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G25">
         <v>824962</v>
       </c>
       <c r="H25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I25">
         <v>5.1</v>
@@ -3170,8 +3542,14 @@
       <c r="Y25">
         <v>0.9649</v>
       </c>
+      <c r="Z25">
+        <v>9</v>
+      </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB25">
+        <v>0.27</v>
       </c>
       <c r="AC25" t="s">
         <v>44</v>
@@ -3190,6 +3568,18 @@
       </c>
       <c r="AH25">
         <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>4.23</v>
+      </c>
+      <c r="AJ25">
+        <v>4.23</v>
+      </c>
+      <c r="AK25">
+        <v>4.23</v>
+      </c>
+      <c r="AL25">
+        <v>4.23</v>
       </c>
       <c r="AM25">
         <v>4.77</v>
@@ -3200,7 +3590,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -3212,13 +3602,13 @@
         <v>-104</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26">
         <v>823098</v>
       </c>
       <c r="H26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I26">
         <v>5.3</v>
@@ -3271,17 +3661,23 @@
       <c r="Y26">
         <v>0.9915</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB26">
+        <v>1.13</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD26">
         <v>6.63</v>
       </c>
       <c r="AE26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF26">
         <v>0.2618</v>
@@ -3291,6 +3687,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>-0.63</v>
+      </c>
+      <c r="AJ26">
+        <v>0.63</v>
+      </c>
+      <c r="AK26">
+        <v>-0.63</v>
+      </c>
+      <c r="AL26">
+        <v>0.63</v>
       </c>
       <c r="AM26">
         <v>6.63</v>
@@ -3301,7 +3709,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3313,13 +3721,13 @@
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27">
         <v>823098</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I27">
         <v>5.8</v>
@@ -3372,11 +3780,17 @@
       <c r="Y27">
         <v>0.9566</v>
       </c>
+      <c r="Z27">
+        <v>7</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB27">
+        <v>-1.73</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD27">
         <v>2.77</v>
@@ -3392,6 +3806,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>4.23</v>
+      </c>
+      <c r="AJ27">
+        <v>4.23</v>
+      </c>
+      <c r="AK27">
+        <v>4.23</v>
+      </c>
+      <c r="AL27">
+        <v>4.23</v>
       </c>
       <c r="AM27">
         <v>2.77</v>
@@ -3402,7 +3828,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3414,13 +3840,13 @@
         <v>-133</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28">
         <v>823181</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I28">
         <v>5.3</v>
@@ -3473,8 +3899,14 @@
       <c r="Y28">
         <v>0.9304</v>
       </c>
+      <c r="Z28">
+        <v>5</v>
+      </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB28">
+        <v>-0.41</v>
       </c>
       <c r="AC28" t="s">
         <v>44</v>
@@ -3493,6 +3925,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0.91</v>
+      </c>
+      <c r="AJ28">
+        <v>0.91</v>
+      </c>
+      <c r="AK28">
+        <v>0.91</v>
+      </c>
+      <c r="AL28">
+        <v>0.91</v>
       </c>
       <c r="AM28">
         <v>4.09</v>
@@ -3503,7 +3947,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>3.5</v>
@@ -3515,13 +3959,13 @@
         <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G29">
         <v>823181</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I29">
         <v>4.8</v>
@@ -3574,11 +4018,17 @@
       <c r="Y29">
         <v>1.0996</v>
       </c>
+      <c r="Z29">
+        <v>2</v>
+      </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB29">
+        <v>1.73</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD29">
         <v>5.23</v>
@@ -3594,6 +4044,18 @@
       </c>
       <c r="AH29">
         <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>-3.23</v>
+      </c>
+      <c r="AJ29">
+        <v>3.23</v>
+      </c>
+      <c r="AK29">
+        <v>-3.23</v>
+      </c>
+      <c r="AL29">
+        <v>3.23</v>
       </c>
       <c r="AM29">
         <v>5.23</v>
@@ -3604,7 +4066,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>5.5</v>
@@ -3622,7 +4084,7 @@
         <v>824233</v>
       </c>
       <c r="H30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I30">
         <v>4.7</v>
@@ -3675,8 +4137,14 @@
       <c r="Y30">
         <v>0.9633</v>
       </c>
+      <c r="Z30">
+        <v>5</v>
+      </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="AB30">
+        <v>-0.3</v>
       </c>
       <c r="AC30" t="s">
         <v>44</v>
@@ -3695,6 +4163,18 @@
       </c>
       <c r="AH30">
         <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>-0.2</v>
+      </c>
+      <c r="AJ30">
+        <v>0.2</v>
+      </c>
+      <c r="AK30">
+        <v>-0.2</v>
+      </c>
+      <c r="AL30">
+        <v>0.2</v>
       </c>
       <c r="AM30">
         <v>5.2</v>
@@ -3705,7 +4185,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3717,7 +4197,7 @@
         <v>-143</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -3749,7 +4229,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3761,7 +4241,7 @@
         <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>
